--- a/data/CTCdata.xlsx
+++ b/data/CTCdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13660"/>
+    <workbookView windowWidth="27660" windowHeight="13040"/>
   </bookViews>
   <sheets>
     <sheet name="Crop_production" sheetId="1" r:id="rId1"/>
@@ -1512,7 +1512,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="4">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>

--- a/data/CTCdata.xlsx
+++ b/data/CTCdata.xlsx
@@ -1512,7 +1512,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="4">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>

--- a/data/CTCdata.xlsx
+++ b/data/CTCdata.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10808"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhongxinzhi/Desktop/CTCv0.1/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECA2938-DE8E-4948-B157-5721900128DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Crop_production" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3708" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="92">
   <si>
     <t>Year</t>
   </si>
@@ -246,37 +252,6 @@
     <t>Composting_tech</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Slow pyrolysis, 450</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, 30mins RT (Alherbawi et al., 2024)</t>
-    </r>
-  </si>
-  <si>
     <t>Cofined windrows (Pergola et al., 2020)</t>
   </si>
   <si>
@@ -480,19 +455,20 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>, 30 mins RT (Ghiat et al., 2022)</t>
+      <t>, 30-90 mins RT (Ferreira et al., 2021)</t>
     </r>
   </si>
   <si>
+    <t>Initial_moisture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final_moisture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Slow pyrolysis, 450</t>
+      <t>Slow pyrolysis, 500</t>
     </r>
     <r>
       <rPr>
@@ -511,21 +487,41 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>, 30-90 mins RT (Ferreira et al., 2021)</t>
+      <t>, 30mins RT (Alherbawi et al., 2024)</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Slow pyrolysis, 550</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 30 mins RT (Ghiat et al., 2022)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,351 +530,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -886,253 +566,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1148,62 +586,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1461,21 +856,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="16.0892857142857" customWidth="1"/>
-    <col min="4" max="5" width="14.0892857142857" customWidth="1"/>
-    <col min="6" max="6" width="12.6339285714286" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +937,7 @@
       <c r="I3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2022</v>
       </c>
@@ -1562,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>2022</v>
       </c>
@@ -1582,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>2022</v>
       </c>
@@ -1602,7 +997,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>2022</v>
       </c>
@@ -1622,7 +1017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -1642,7 +1037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -1662,7 +1057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>2022</v>
       </c>
@@ -1682,7 +1077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>2022</v>
       </c>
@@ -1702,7 +1097,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>2022</v>
       </c>
@@ -1722,7 +1117,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>2022</v>
       </c>
@@ -1742,7 +1137,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>2022</v>
       </c>
@@ -1762,7 +1157,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>2022</v>
       </c>
@@ -1782,7 +1177,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>2022</v>
       </c>
@@ -1983,24 +1378,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G649"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.1785714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" style="3" customWidth="1"/>
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1785714285714" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="12.1785714285714" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2047,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>29.585</v>
+        <v>29.585000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2093,7 +1487,7 @@
         <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>16.769</v>
+        <v>16.768999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2116,7 +1510,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>20.859</v>
+        <v>20.859000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2139,7 +1533,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>45.5409101797494</v>
+        <v>45.540910179749403</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2162,7 +1556,7 @@
         <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>13.9614469164195</v>
+        <v>13.961446916419501</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2185,7 +1579,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>19.9449241663136</v>
+        <v>19.944924166313601</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2208,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>11.6345390970163</v>
+        <v>11.634539097016299</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2231,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2254,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2277,7 +1671,7 @@
         <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>652.47156</v>
+        <v>652.47155999999995</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2300,7 +1694,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>239.94828</v>
+        <v>239.94828000000001</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2392,7 +1786,7 @@
         <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>6.98072345820976</v>
+        <v>6.9807234582097601</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2415,7 +1809,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="1">
-        <v>569.232</v>
+        <v>569.23199999999997</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2438,7 +1832,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>10.3048774859287</v>
+        <v>10.304877485928699</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2484,7 +1878,7 @@
         <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>3.965</v>
+        <v>3.9649999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2507,7 +1901,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="1">
-        <v>3.965</v>
+        <v>3.9649999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2553,7 +1947,7 @@
         <v>9</v>
       </c>
       <c r="G24" s="1">
-        <v>28.975</v>
+        <v>28.975000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2599,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="G26" s="1">
-        <v>89.208</v>
+        <v>89.207999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2645,7 +2039,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="1">
-        <v>167.088</v>
+        <v>167.08799999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2668,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="G29" s="1">
-        <v>727.824</v>
+        <v>727.82399999999996</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2691,7 +2085,7 @@
         <v>9</v>
       </c>
       <c r="G30" s="1">
-        <v>2.454</v>
+        <v>2.4540000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2714,7 +2108,7 @@
         <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>0.818</v>
+        <v>0.81799999999999995</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2737,7 +2131,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>33.947</v>
+        <v>33.947000000000003</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2760,7 +2154,7 @@
         <v>9</v>
       </c>
       <c r="G33" s="1">
-        <v>2.454</v>
+        <v>2.4540000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2783,7 +2177,7 @@
         <v>9</v>
       </c>
       <c r="G34" s="1">
-        <v>0.818</v>
+        <v>0.81799999999999995</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2921,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="G40" s="1">
-        <v>9.30763127761301</v>
+        <v>9.3076312776130106</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2944,7 +2338,7 @@
         <v>9</v>
       </c>
       <c r="G41" s="1">
-        <v>0.332415402771893</v>
+        <v>0.33241540277189302</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2967,7 +2361,7 @@
         <v>9</v>
       </c>
       <c r="G42" s="1">
-        <v>0.332415402771893</v>
+        <v>0.33241540277189302</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2990,7 +2384,7 @@
         <v>9</v>
       </c>
       <c r="G43" s="1">
-        <v>0.664830805543786</v>
+        <v>0.66483080554378604</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3036,7 +2430,7 @@
         <v>9</v>
       </c>
       <c r="G45" s="1">
-        <v>67.8127421654662</v>
+        <v>67.812742165466204</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3059,7 +2453,7 @@
         <v>9</v>
       </c>
       <c r="G46" s="1">
-        <v>0.664830805543786</v>
+        <v>0.66483080554378604</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3174,7 +2568,7 @@
         <v>9</v>
       </c>
       <c r="G51" s="1">
-        <v>2.23906005636294</v>
+        <v>2.2390600563629399</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3197,7 +2591,7 @@
         <v>9</v>
       </c>
       <c r="G52" s="1">
-        <v>2.74583536922408</v>
+        <v>2.7458353692240798</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3220,7 +2614,7 @@
         <v>9</v>
       </c>
       <c r="G53" s="1">
-        <v>3.85059415714689</v>
+        <v>3.8505941571468898</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3243,7 +2637,7 @@
         <v>9</v>
       </c>
       <c r="G54" s="1">
-        <v>3.90576</v>
+        <v>3.9057599999999999</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3266,7 +2660,7 @@
         <v>9</v>
       </c>
       <c r="G55" s="1">
-        <v>1.77276</v>
+        <v>1.7727599999999999</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3289,7 +2683,7 @@
         <v>9</v>
       </c>
       <c r="G56" s="1">
-        <v>6.00564195710251</v>
+        <v>6.0056419571025099</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3312,7 +2706,7 @@
         <v>9</v>
       </c>
       <c r="G57" s="1">
-        <v>18.061573448</v>
+        <v>18.061573448000001</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3335,7 +2729,7 @@
         <v>9</v>
       </c>
       <c r="G58" s="1">
-        <v>0.0221635517348976</v>
+        <v>2.2163551734897601E-2</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3358,7 +2752,7 @@
         <v>9</v>
       </c>
       <c r="G59" s="1">
-        <v>1.25699482823076</v>
+        <v>1.2569948282307599</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3381,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="G60" s="1">
-        <v>18.2962580553588</v>
+        <v>18.296258055358798</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3404,7 +2798,7 @@
         <v>9</v>
       </c>
       <c r="G61" s="1">
-        <v>1.25699482823076</v>
+        <v>1.2569948282307599</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3427,7 +2821,7 @@
         <v>9</v>
       </c>
       <c r="G62" s="1">
-        <v>7.68163506141019</v>
+        <v>7.6816350614101898</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3450,7 +2844,7 @@
         <v>9</v>
       </c>
       <c r="G63" s="1">
-        <v>1.67599310430768</v>
+        <v>1.6759931043076799</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3473,7 +2867,7 @@
         <v>9</v>
       </c>
       <c r="G64" s="1">
-        <v>0.83884226745</v>
+        <v>0.83884226745000001</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3496,7 +2890,7 @@
         <v>9</v>
       </c>
       <c r="G65" s="1">
-        <v>27.6770900638</v>
+        <v>27.677090063800001</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3519,7 +2913,7 @@
         <v>9</v>
       </c>
       <c r="G66" s="1">
-        <v>5.96412974596</v>
+        <v>5.9641297459600002</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3542,7 +2936,7 @@
         <v>9</v>
       </c>
       <c r="G67" s="1">
-        <v>13.49334011598</v>
+        <v>13.493340115980001</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3565,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="G68" s="1">
-        <v>1.15369893363</v>
+        <v>1.1536989336300001</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3588,7 +2982,7 @@
         <v>9</v>
       </c>
       <c r="G69" s="1">
-        <v>3.09269523980778</v>
+        <v>3.0926952398077798</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3634,7 +3028,7 @@
         <v>9</v>
       </c>
       <c r="G71" s="1">
-        <v>0.471219326651705</v>
+        <v>0.47121932665170502</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3657,7 +3051,7 @@
         <v>9</v>
       </c>
       <c r="G72" s="1">
-        <v>0.256322318013775</v>
+        <v>0.25632231801377497</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3680,7 +3074,7 @@
         <v>9</v>
       </c>
       <c r="G73" s="1">
-        <v>1.11127895151726</v>
+        <v>1.1112789515172601</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3703,7 +3097,7 @@
         <v>9</v>
       </c>
       <c r="G74" s="1">
-        <v>3.51645</v>
+        <v>3.5164499999999999</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3726,7 +3120,7 @@
         <v>9</v>
       </c>
       <c r="G75" s="1">
-        <v>5.36628</v>
+        <v>5.3662799999999997</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3749,7 +3143,7 @@
         <v>9</v>
       </c>
       <c r="G76" s="1">
-        <v>3.05804</v>
+        <v>3.0580400000000001</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3841,7 +3235,7 @@
         <v>9</v>
       </c>
       <c r="G80" s="1">
-        <v>0.428</v>
+        <v>0.42799999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3864,7 +3258,7 @@
         <v>9</v>
       </c>
       <c r="G81" s="1">
-        <v>0.1819</v>
+        <v>0.18190000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3887,7 +3281,7 @@
         <v>9</v>
       </c>
       <c r="G82" s="1">
-        <v>0.36432</v>
+        <v>0.36431999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3910,7 +3304,7 @@
         <v>9</v>
       </c>
       <c r="G83" s="1">
-        <v>1.02212</v>
+        <v>1.0221199999999999</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3956,7 +3350,7 @@
         <v>9</v>
       </c>
       <c r="G85" s="1">
-        <v>1.09691</v>
+        <v>1.0969100000000001</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3979,7 +3373,7 @@
         <v>9</v>
       </c>
       <c r="G86" s="1">
-        <v>48.8464253670096</v>
+        <v>48.846425367009601</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4025,7 +3419,7 @@
         <v>9</v>
       </c>
       <c r="G88" s="1">
-        <v>0.309790297571696</v>
+        <v>0.30979029757169602</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4071,7 +3465,7 @@
         <v>9</v>
       </c>
       <c r="G90" s="1">
-        <v>23.777</v>
+        <v>23.777000000000001</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4094,7 +3488,7 @@
         <v>9</v>
       </c>
       <c r="G91" s="1">
-        <v>3.51168</v>
+        <v>3.5116800000000001</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4117,7 +3511,7 @@
         <v>9</v>
       </c>
       <c r="G92" s="1">
-        <v>0.9384</v>
+        <v>0.93840000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4163,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="G94" s="1">
-        <v>0.9028</v>
+        <v>0.90280000000000005</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4186,7 +3580,7 @@
         <v>9</v>
       </c>
       <c r="G95" s="1">
-        <v>0.814</v>
+        <v>0.81399999999999995</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4232,7 +3626,7 @@
         <v>9</v>
       </c>
       <c r="G97" s="1">
-        <v>0.74438</v>
+        <v>0.74438000000000004</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4255,7 +3649,7 @@
         <v>9</v>
       </c>
       <c r="G98" s="1">
-        <v>5.6846</v>
+        <v>5.6845999999999997</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4278,7 +3672,7 @@
         <v>9</v>
       </c>
       <c r="G99" s="1">
-        <v>1.03116</v>
+        <v>1.0311600000000001</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4301,7 +3695,7 @@
         <v>9</v>
       </c>
       <c r="G100" s="1">
-        <v>8.5097</v>
+        <v>8.5097000000000005</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4324,7 +3718,7 @@
         <v>9</v>
       </c>
       <c r="G101" s="1">
-        <v>1.7372</v>
+        <v>1.7372000000000001</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4370,7 +3764,7 @@
         <v>9</v>
       </c>
       <c r="G103" s="1">
-        <v>0.04275</v>
+        <v>4.2750000000000003E-2</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4393,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="G104" s="1">
-        <v>2.72101</v>
+        <v>2.7210100000000002</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4416,7 +3810,7 @@
         <v>9</v>
       </c>
       <c r="G105" s="1">
-        <v>0.89666</v>
+        <v>0.89666000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4439,7 +3833,7 @@
         <v>9</v>
       </c>
       <c r="G106" s="1">
-        <v>2.1543</v>
+        <v>2.1543000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4508,7 +3902,7 @@
         <v>9</v>
       </c>
       <c r="G109" s="1">
-        <v>0.00664830805543786</v>
+        <v>6.6483080554378604E-3</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4531,7 +3925,7 @@
         <v>9</v>
       </c>
       <c r="G110" s="1">
-        <v>1.57685</v>
+        <v>1.5768500000000001</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4554,7 +3948,7 @@
         <v>9</v>
       </c>
       <c r="G111" s="1">
-        <v>2.26615</v>
+        <v>2.2661500000000001</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4577,7 +3971,7 @@
         <v>9</v>
       </c>
       <c r="G112" s="1">
-        <v>3.765</v>
+        <v>3.7650000000000001</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4600,7 +3994,7 @@
         <v>9</v>
       </c>
       <c r="G113" s="1">
-        <v>2.94172</v>
+        <v>2.9417200000000001</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4623,7 +4017,7 @@
         <v>9</v>
       </c>
       <c r="G114" s="1">
-        <v>0.062748</v>
+        <v>6.2747999999999998E-2</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4646,7 +4040,7 @@
         <v>9</v>
       </c>
       <c r="G115" s="1">
-        <v>0.310254</v>
+        <v>0.31025399999999997</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4669,7 +4063,7 @@
         <v>9</v>
       </c>
       <c r="G116" s="1">
-        <v>0.01792</v>
+        <v>1.7919999999999998E-2</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4692,7 +4086,7 @@
         <v>9</v>
       </c>
       <c r="G117" s="1">
-        <v>0.0448</v>
+        <v>4.48E-2</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4715,7 +4109,7 @@
         <v>9</v>
       </c>
       <c r="G118" s="1">
-        <v>0.254571640211552</v>
+        <v>0.25457164021155199</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4761,7 +4155,7 @@
         <v>9</v>
       </c>
       <c r="G120" s="1">
-        <v>0.176616788649493</v>
+        <v>0.17661678864949301</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4784,7 +4178,7 @@
         <v>9</v>
       </c>
       <c r="G121" s="1">
-        <v>0.072816089343</v>
+        <v>7.2816089343000004E-2</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4807,7 +4201,7 @@
         <v>9</v>
       </c>
       <c r="G122" s="1">
-        <v>4.2873830847</v>
+        <v>4.2873830847000001</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4830,7 +4224,7 @@
         <v>9</v>
       </c>
       <c r="G123" s="1">
-        <v>0.00254502983</v>
+        <v>2.54502983E-3</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4853,7 +4247,7 @@
         <v>9</v>
       </c>
       <c r="G124" s="1">
-        <v>2.40236887527</v>
+        <v>2.4023688752700001</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4899,7 +4293,7 @@
         <v>9</v>
       </c>
       <c r="G126" s="1">
-        <v>0.13239707188</v>
+        <v>0.13239707187999999</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4922,7 +4316,7 @@
         <v>9</v>
       </c>
       <c r="G127" s="1">
-        <v>5.00742815139</v>
+        <v>5.0074281513900001</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4945,7 +4339,7 @@
         <v>9</v>
       </c>
       <c r="G128" s="1">
-        <v>8.1809169561</v>
+        <v>8.1809169561000008</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4968,7 +4362,7 @@
         <v>9</v>
       </c>
       <c r="G129" s="1">
-        <v>0.129904115366</v>
+        <v>0.12990411536599999</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4991,7 +4385,7 @@
         <v>9</v>
       </c>
       <c r="G130" s="1">
-        <v>2.22731375963</v>
+        <v>2.2273137596299999</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -5014,7 +4408,7 @@
         <v>9</v>
       </c>
       <c r="G131" s="1">
-        <v>0.0234424288</v>
+        <v>2.3442428800000002E-2</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -5037,7 +4431,7 @@
         <v>9</v>
       </c>
       <c r="G132" s="1">
-        <v>0.938003746213183</v>
+        <v>0.93800374621318305</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -5060,7 +4454,7 @@
         <v>9</v>
       </c>
       <c r="G133" s="1">
-        <v>0.006227827037</v>
+        <v>6.2278270370000003E-3</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5083,7 +4477,7 @@
         <v>9</v>
       </c>
       <c r="G134" s="1">
-        <v>0.02795142061</v>
+        <v>2.795142061E-2</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -5106,7 +4500,7 @@
         <v>9</v>
       </c>
       <c r="G135" s="1">
-        <v>0.145882019316</v>
+        <v>0.14588201931600001</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -5129,7 +4523,7 @@
         <v>9</v>
       </c>
       <c r="G136" s="1">
-        <v>0.521525215</v>
+        <v>0.52152521500000004</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5175,7 +4569,7 @@
         <v>9</v>
       </c>
       <c r="G138" s="1">
-        <v>0.779224865034</v>
+        <v>0.77922486503400001</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5221,7 +4615,7 @@
         <v>9</v>
       </c>
       <c r="G140" s="1">
-        <v>0.002914758217</v>
+        <v>2.9147582169999999E-3</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -5244,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="G141" s="1">
-        <v>5.24906364016342</v>
+        <v>5.2490636401634196</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5267,7 +4661,7 @@
         <v>9</v>
       </c>
       <c r="G142" s="1">
-        <v>0.01441256488</v>
+        <v>1.4412564879999999E-2</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5290,7 +4684,7 @@
         <v>9</v>
       </c>
       <c r="G143" s="1">
-        <v>0.591</v>
+        <v>0.59099999999999997</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5313,7 +4707,7 @@
         <v>9</v>
       </c>
       <c r="G144" s="1">
-        <v>1.182</v>
+        <v>1.1819999999999999</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5405,7 +4799,7 @@
         <v>9</v>
       </c>
       <c r="G148" s="1">
-        <v>0.0067768788773</v>
+        <v>6.7768788773000001E-3</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5428,7 +4822,7 @@
         <v>9</v>
       </c>
       <c r="G149" s="1">
-        <v>0.0170042067132</v>
+        <v>1.70042067132E-2</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5451,7 +4845,7 @@
         <v>9</v>
       </c>
       <c r="G150" s="1">
-        <v>0.0056454169926</v>
+        <v>5.6454169925999999E-3</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5474,7 +4868,7 @@
         <v>9</v>
       </c>
       <c r="G151" s="1">
-        <v>0.0056793948603</v>
+        <v>5.6793948602999996E-3</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5497,7 +4891,7 @@
         <v>9</v>
       </c>
       <c r="G152" s="1">
-        <v>0.0045479329756</v>
+        <v>4.5479329756000003E-3</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5520,7 +4914,7 @@
         <v>9</v>
       </c>
       <c r="G153" s="1">
-        <v>1.873476462414</v>
+        <v>1.8734764624139999</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5589,7 +4983,7 @@
         <v>9</v>
       </c>
       <c r="G156" s="1">
-        <v>0.009888426314</v>
+        <v>9.8884263140000001E-3</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5635,7 +5029,7 @@
         <v>9</v>
       </c>
       <c r="G158" s="1">
-        <v>2.53950420216</v>
+        <v>2.5395042021599998</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5658,7 +5052,7 @@
         <v>9</v>
       </c>
       <c r="G159" s="1">
-        <v>6.640441339704</v>
+        <v>6.6404413397040001</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5704,7 +5098,7 @@
         <v>9</v>
       </c>
       <c r="G161" s="1">
-        <v>3.23796611276</v>
+        <v>3.2379661127600001</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5865,7 +5259,7 @@
         <v>9</v>
       </c>
       <c r="G168" s="1">
-        <v>6.442513733692</v>
+        <v>6.4425137336920004</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5888,7 +5282,7 @@
         <v>9</v>
       </c>
       <c r="G169" s="1">
-        <v>0.211487641696</v>
+        <v>0.21148764169600001</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5934,7 +5328,7 @@
         <v>9</v>
       </c>
       <c r="G171" s="1">
-        <v>3.944315966158</v>
+        <v>3.9443159661579998</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5957,7 +5351,7 @@
         <v>9</v>
       </c>
       <c r="G172" s="1">
-        <v>0.069305071772</v>
+        <v>6.9305071772000001E-2</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5980,7 +5374,7 @@
         <v>9</v>
       </c>
       <c r="G173" s="1">
-        <v>0.04493988996</v>
+        <v>4.493988996E-2</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -6003,7 +5397,7 @@
         <v>9</v>
       </c>
       <c r="G174" s="1">
-        <v>0.04735401617</v>
+        <v>4.7354016169999999E-2</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -6026,7 +5420,7 @@
         <v>9</v>
       </c>
       <c r="G175" s="1">
-        <v>9.8409073472</v>
+        <v>9.8409073471999999</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -6049,7 +5443,7 @@
         <v>9</v>
       </c>
       <c r="G176" s="1">
-        <v>0.47892551954</v>
+        <v>0.47892551954000001</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -6118,7 +5512,7 @@
         <v>9</v>
       </c>
       <c r="G179" s="1">
-        <v>0.260737223516</v>
+        <v>0.26073722351599998</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6141,7 +5535,7 @@
         <v>9</v>
       </c>
       <c r="G180" s="1">
-        <v>3.076668271199</v>
+        <v>3.0766682711989999</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6164,7 +5558,7 @@
         <v>9</v>
       </c>
       <c r="G181" s="1">
-        <v>0.088718782242</v>
+        <v>8.8718782241999999E-2</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6187,7 +5581,7 @@
         <v>9</v>
       </c>
       <c r="G182" s="1">
-        <v>0.066732626504</v>
+        <v>6.6732626503999998E-2</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6210,7 +5604,7 @@
         <v>9</v>
       </c>
       <c r="G183" s="1">
-        <v>0.29032639767</v>
+        <v>0.29032639767000001</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6256,7 +5650,7 @@
         <v>9</v>
       </c>
       <c r="G185" s="1">
-        <v>2.82068741654</v>
+        <v>2.8206874165400002</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6302,7 +5696,7 @@
         <v>9</v>
       </c>
       <c r="G187" s="1">
-        <v>0.03111159177</v>
+        <v>3.1111591769999999E-2</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6394,7 +5788,7 @@
         <v>9</v>
       </c>
       <c r="G191" s="1">
-        <v>0.185022413182836</v>
+        <v>0.18502241318283599</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6440,7 +5834,7 @@
         <v>9</v>
       </c>
       <c r="G193" s="1">
-        <v>0.29594089532</v>
+        <v>0.29594089532000001</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6463,7 +5857,7 @@
         <v>9</v>
       </c>
       <c r="G194" s="1">
-        <v>0.54521891088</v>
+        <v>0.54521891087999996</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6486,7 +5880,7 @@
         <v>9</v>
       </c>
       <c r="G195" s="1">
-        <v>4.28039824009</v>
+        <v>4.2803982400900003</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6509,7 +5903,7 @@
         <v>9</v>
       </c>
       <c r="G196" s="1">
-        <v>0.47737353965</v>
+        <v>0.47737353965000001</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6532,7 +5926,7 @@
         <v>9</v>
       </c>
       <c r="G197" s="1">
-        <v>0.0982376416</v>
+        <v>9.8237641599999995E-2</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6555,7 +5949,7 @@
         <v>9</v>
       </c>
       <c r="G198" s="1">
-        <v>0.2295272</v>
+        <v>0.22952719999999999</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6578,7 +5972,7 @@
         <v>9</v>
       </c>
       <c r="G199" s="1">
-        <v>0.055373437</v>
+        <v>5.5373436999999998E-2</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6601,7 +5995,7 @@
         <v>9</v>
       </c>
       <c r="G200" s="1">
-        <v>3.306913134</v>
+        <v>3.3069131340000002</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6624,7 +6018,7 @@
         <v>9</v>
       </c>
       <c r="G201" s="1">
-        <v>0.144889045</v>
+        <v>0.14488904499999999</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6647,7 +6041,7 @@
         <v>9</v>
       </c>
       <c r="G202" s="1">
-        <v>0.216903204</v>
+        <v>0.21690320399999999</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6670,7 +6064,7 @@
         <v>9</v>
       </c>
       <c r="G203" s="1">
-        <v>0.047688005617</v>
+        <v>4.7688005616999998E-2</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6693,7 +6087,7 @@
         <v>9</v>
       </c>
       <c r="G204" s="1">
-        <v>0.0824576466</v>
+        <v>8.2457646600000004E-2</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6716,7 +6110,7 @@
         <v>9</v>
       </c>
       <c r="G205" s="1">
-        <v>3.640917385623</v>
+        <v>3.6409173856230002</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6739,7 +6133,7 @@
         <v>9</v>
       </c>
       <c r="G206" s="1">
-        <v>0.074624170173</v>
+        <v>7.4624170173000007E-2</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6762,7 +6156,7 @@
         <v>9</v>
       </c>
       <c r="G207" s="1">
-        <v>0.03023447042</v>
+        <v>3.0234470419999999E-2</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6785,7 +6179,7 @@
         <v>9</v>
       </c>
       <c r="G208" s="1">
-        <v>0.329115216</v>
+        <v>0.32911521599999999</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6808,7 +6202,7 @@
         <v>9</v>
       </c>
       <c r="G209" s="1">
-        <v>0.793229276</v>
+        <v>0.79322927600000004</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6831,7 +6225,7 @@
         <v>9</v>
       </c>
       <c r="G210" s="1">
-        <v>1.251923242</v>
+        <v>1.2519232419999999</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6854,7 +6248,7 @@
         <v>9</v>
       </c>
       <c r="G211" s="1">
-        <v>0.446846766</v>
+        <v>0.44684676600000001</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6900,7 +6294,7 @@
         <v>9</v>
       </c>
       <c r="G213" s="1">
-        <v>0.0411682537744219</v>
+        <v>4.1168253774421897E-2</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6923,7 +6317,7 @@
         <v>9</v>
       </c>
       <c r="G214" s="1">
-        <v>0.418145977704116</v>
+        <v>0.41814597770411599</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6946,7 +6340,7 @@
         <v>9</v>
       </c>
       <c r="G215" s="1">
-        <v>0.0258778771528733</v>
+        <v>2.5877877152873301E-2</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6969,7 +6363,7 @@
         <v>9</v>
       </c>
       <c r="G216" s="1">
-        <v>0.0345842272481083</v>
+        <v>3.45842272481083E-2</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6992,7 +6386,7 @@
         <v>9</v>
       </c>
       <c r="G217" s="1">
-        <v>1.98897894377876</v>
+        <v>1.9889789437787599</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7015,7 +6409,7 @@
         <v>9</v>
       </c>
       <c r="G218" s="1">
-        <v>0.12872152216</v>
+        <v>0.12872152215999999</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7038,7 +6432,7 @@
         <v>9</v>
       </c>
       <c r="G219" s="1">
-        <v>0.035201266065</v>
+        <v>3.5201266065E-2</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7107,7 +6501,7 @@
         <v>9</v>
       </c>
       <c r="G222" s="1">
-        <v>0.186627127855</v>
+        <v>0.18662712785499999</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7153,7 +6547,7 @@
         <v>9</v>
       </c>
       <c r="G224" s="1">
-        <v>1.13984055350298</v>
+        <v>1.1398405535029801</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7199,7 +6593,7 @@
         <v>9</v>
       </c>
       <c r="G226" s="1">
-        <v>8.81696785872759</v>
+        <v>8.8169678587275904</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7222,7 +6616,7 @@
         <v>9</v>
       </c>
       <c r="G227" s="1">
-        <v>5.00273007158639</v>
+        <v>5.0027300715863898</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7245,7 +6639,7 @@
         <v>9</v>
       </c>
       <c r="G228" s="1">
-        <v>0.010567242224</v>
+        <v>1.0567242224E-2</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7268,7 +6662,7 @@
         <v>9</v>
       </c>
       <c r="G229" s="1">
-        <v>0.053070211376</v>
+        <v>5.3070211376000001E-2</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7291,7 +6685,7 @@
         <v>9</v>
       </c>
       <c r="G230" s="1">
-        <v>0.021171711736</v>
+        <v>2.1171711736E-2</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7314,7 +6708,7 @@
         <v>9</v>
       </c>
       <c r="G231" s="1">
-        <v>0.025591127072</v>
+        <v>2.5591127072000001E-2</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -7337,7 +6731,7 @@
         <v>9</v>
       </c>
       <c r="G232" s="1">
-        <v>0.047571203568</v>
+        <v>4.7571203568000001E-2</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -7383,7 +6777,7 @@
         <v>9</v>
       </c>
       <c r="G234" s="1">
-        <v>0.063884563358</v>
+        <v>6.3884563357999996E-2</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7406,7 +6800,7 @@
         <v>9</v>
       </c>
       <c r="G235" s="1">
-        <v>0.136696646464</v>
+        <v>0.13669664646400001</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7429,7 +6823,7 @@
         <v>9</v>
       </c>
       <c r="G236" s="1">
-        <v>0.013343282204</v>
+        <v>1.3343282204000001E-2</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7521,7 +6915,7 @@
         <v>9</v>
       </c>
       <c r="G240" s="1">
-        <v>4.60794508556844</v>
+        <v>4.6079450855684403</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7544,7 +6938,7 @@
         <v>9</v>
       </c>
       <c r="G241" s="1">
-        <v>0.00619924310160227</v>
+        <v>6.1992431016022701E-3</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7590,7 +6984,7 @@
         <v>9</v>
       </c>
       <c r="G243" s="1">
-        <v>0.000126009117130468</v>
+        <v>1.2600911713046801E-4</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7613,7 +7007,7 @@
         <v>9</v>
       </c>
       <c r="G244" s="1">
-        <v>0.0104587567218288</v>
+        <v>1.0458756721828799E-2</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7636,7 +7030,7 @@
         <v>9</v>
       </c>
       <c r="G245" s="1">
-        <v>0.000698777831359868</v>
+        <v>6.9877783135986803E-4</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7659,7 +7053,7 @@
         <v>9</v>
       </c>
       <c r="G246" s="1">
-        <v>0.00197032437694914</v>
+        <v>1.9703243769491402E-3</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7682,7 +7076,7 @@
         <v>9</v>
       </c>
       <c r="G247" s="1">
-        <v>0.0104530290346865</v>
+        <v>1.0453029034686499E-2</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7705,7 +7099,7 @@
         <v>9</v>
       </c>
       <c r="G248" s="1">
-        <v>0.06568810948</v>
+        <v>6.5688109480000006E-2</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7728,7 +7122,7 @@
         <v>9</v>
       </c>
       <c r="G249" s="1">
-        <v>0.02721604536</v>
+        <v>2.721604536E-2</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7751,7 +7145,7 @@
         <v>9</v>
       </c>
       <c r="G250" s="1">
-        <v>0.002906404872</v>
+        <v>2.906404872E-3</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7774,7 +7168,7 @@
         <v>9</v>
       </c>
       <c r="G251" s="1">
-        <v>0.000620158784</v>
+        <v>6.2015878400000001E-4</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7797,7 +7191,7 @@
         <v>9</v>
       </c>
       <c r="G252" s="1">
-        <v>0.006764626736</v>
+        <v>6.7646267359999998E-3</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7820,7 +7214,7 @@
         <v>9</v>
       </c>
       <c r="G253" s="1">
-        <v>0.000758878512</v>
+        <v>7.5887851199999995E-4</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7843,7 +7237,7 @@
         <v>9</v>
       </c>
       <c r="G254" s="1">
-        <v>0.000391679232</v>
+        <v>3.9167923200000002E-4</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7866,7 +7260,7 @@
         <v>9</v>
       </c>
       <c r="G255" s="1">
-        <v>0.001232157584</v>
+        <v>1.2321575840000001E-3</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7889,7 +7283,7 @@
         <v>9</v>
       </c>
       <c r="G256" s="1">
-        <v>0.00026544</v>
+        <v>2.6543999999999998E-4</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7912,7 +7306,7 @@
         <v>9</v>
       </c>
       <c r="G257" s="1">
-        <v>0.00165347</v>
+        <v>1.65347E-3</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7935,7 +7329,7 @@
         <v>9</v>
       </c>
       <c r="G258" s="1">
-        <v>0.00139356</v>
+        <v>1.3935600000000001E-3</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7958,7 +7352,7 @@
         <v>9</v>
       </c>
       <c r="G259" s="1">
-        <v>0.00072996</v>
+        <v>7.2995999999999998E-4</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7981,7 +7375,7 @@
         <v>9</v>
       </c>
       <c r="G260" s="1">
-        <v>0.02575874</v>
+        <v>2.5758739999999999E-2</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -8004,7 +7398,7 @@
         <v>9</v>
       </c>
       <c r="G261" s="1">
-        <v>1.106e-5</v>
+        <v>1.1060000000000001E-5</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -8050,7 +7444,7 @@
         <v>9</v>
       </c>
       <c r="G263" s="1">
-        <v>0.0003871</v>
+        <v>3.8709999999999998E-4</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -8073,7 +7467,7 @@
         <v>9</v>
       </c>
       <c r="G264" s="1">
-        <v>6.636e-5</v>
+        <v>6.6359999999999995E-5</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -8096,7 +7490,7 @@
         <v>9</v>
       </c>
       <c r="G265" s="1">
-        <v>0.00010507</v>
+        <v>1.0507E-4</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -8142,7 +7536,7 @@
         <v>9</v>
       </c>
       <c r="G267" s="1">
-        <v>0.001322076672</v>
+        <v>1.3220766720000001E-3</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -8165,7 +7559,7 @@
         <v>9</v>
       </c>
       <c r="G268" s="1">
-        <v>0.003745883904</v>
+        <v>3.7458839040000001E-3</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -8234,7 +7628,7 @@
         <v>9</v>
       </c>
       <c r="G271" s="1">
-        <v>1.46522406613399</v>
+        <v>1.4652240661339899</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -8257,7 +7651,7 @@
         <v>9</v>
       </c>
       <c r="G272" s="1">
-        <v>3.56750207406536</v>
+        <v>3.5675020740653598</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -8280,7 +7674,7 @@
         <v>9</v>
       </c>
       <c r="G273" s="1">
-        <v>0.871556317875583</v>
+        <v>0.87155631787558296</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -8303,7 +7697,7 @@
         <v>9</v>
       </c>
       <c r="G274" s="1">
-        <v>0.0642856818872127</v>
+        <v>6.4285681887212703E-2</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -8326,7 +7720,7 @@
         <v>9</v>
       </c>
       <c r="G275" s="1">
-        <v>0.520401956869495</v>
+        <v>0.52040195686949497</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -8349,7 +7743,7 @@
         <v>9</v>
       </c>
       <c r="G276" s="1">
-        <v>0.28135908150248</v>
+        <v>0.28135908150248001</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -8372,7 +7766,7 @@
         <v>9</v>
       </c>
       <c r="G277" s="1">
-        <v>9.504</v>
+        <v>9.5039999999999996</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -8441,7 +7835,7 @@
         <v>9</v>
       </c>
       <c r="G280" s="1">
-        <v>1.739275707456</v>
+        <v>1.7392757074559999</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -8464,7 +7858,7 @@
         <v>9</v>
       </c>
       <c r="G281" s="1">
-        <v>0.153864470592</v>
+        <v>0.15386447059200001</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -8487,7 +7881,7 @@
         <v>9</v>
       </c>
       <c r="G282" s="1">
-        <v>2.468936941632</v>
+        <v>2.4689369416320002</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -8510,7 +7904,7 @@
         <v>9</v>
       </c>
       <c r="G283" s="1">
-        <v>0.513139947264</v>
+        <v>0.51313994726400003</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8533,7 +7927,7 @@
         <v>9</v>
       </c>
       <c r="G284" s="1">
-        <v>0.26935971552</v>
+        <v>0.26935971551999999</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8556,7 +7950,7 @@
         <v>9</v>
       </c>
       <c r="G285" s="1">
-        <v>0.008780408672</v>
+        <v>8.7804086720000007E-3</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8602,7 +7996,7 @@
         <v>9</v>
       </c>
       <c r="G287" s="1">
-        <v>0.147736045912</v>
+        <v>0.14773604591200001</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8648,7 +8042,7 @@
         <v>9</v>
       </c>
       <c r="G289" s="1">
-        <v>0.047653269216</v>
+        <v>4.7653269216000001E-2</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8671,7 +8065,7 @@
         <v>9</v>
       </c>
       <c r="G290" s="1">
-        <v>0.005093013128</v>
+        <v>5.0930131279999999E-3</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8694,7 +8088,7 @@
         <v>9</v>
       </c>
       <c r="G291" s="1">
-        <v>0.0508618936122344</v>
+        <v>5.08618936122344E-2</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8717,7 +8111,7 @@
         <v>9</v>
       </c>
       <c r="G292" s="1">
-        <v>0.027105194863346</v>
+        <v>2.7105194863346001E-2</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8740,7 +8134,7 @@
         <v>9</v>
       </c>
       <c r="G293" s="1">
-        <v>0.18846746025268</v>
+        <v>0.18846746025267999</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8809,7 +8203,7 @@
         <v>9</v>
       </c>
       <c r="G296" s="1">
-        <v>0.27940333806</v>
+        <v>0.27940333806000001</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -8832,7 +8226,7 @@
         <v>9</v>
       </c>
       <c r="G297" s="1">
-        <v>0.11800944</v>
+        <v>0.11800943999999999</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -8855,7 +8249,7 @@
         <v>9</v>
       </c>
       <c r="G298" s="1">
-        <v>0.28442484</v>
+        <v>0.28442484000000001</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -8901,7 +8295,7 @@
         <v>9</v>
       </c>
       <c r="G300" s="1">
-        <v>0.16022394</v>
+        <v>0.16022394000000001</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -8924,7 +8318,7 @@
         <v>9</v>
       </c>
       <c r="G301" s="1">
-        <v>0.67974372</v>
+        <v>0.67974372000000005</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -8947,7 +8341,7 @@
         <v>9</v>
       </c>
       <c r="G302" s="1">
-        <v>3.96797</v>
+        <v>3.9679700000000002</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -8970,7 +8364,7 @@
         <v>9</v>
       </c>
       <c r="G303" s="1">
-        <v>0.87872</v>
+        <v>0.87871999999999995</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -8993,7 +8387,7 @@
         <v>9</v>
       </c>
       <c r="G304" s="1">
-        <v>1.09643544295</v>
+        <v>1.0964354429500001</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -9062,7 +8456,7 @@
         <v>9</v>
       </c>
       <c r="G307" s="1">
-        <v>0.023979665782</v>
+        <v>2.3979665782E-2</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -9085,7 +8479,7 @@
         <v>9</v>
       </c>
       <c r="G308" s="1">
-        <v>0.001701260089</v>
+        <v>1.7012600890000001E-3</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -9315,7 +8709,7 @@
         <v>9</v>
       </c>
       <c r="G318" s="1">
-        <v>0.02656</v>
+        <v>2.656E-2</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -9338,7 +8732,7 @@
         <v>9</v>
       </c>
       <c r="G319" s="1">
-        <v>0.0664</v>
+        <v>6.6400000000000001E-2</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -9361,7 +8755,7 @@
         <v>9</v>
       </c>
       <c r="G320" s="1">
-        <v>0.02136148009</v>
+        <v>2.1361480089999999E-2</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -9384,7 +8778,7 @@
         <v>9</v>
       </c>
       <c r="G321" s="1">
-        <v>0.015662162582</v>
+        <v>1.5662162582000001E-2</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -9407,7 +8801,7 @@
         <v>9</v>
       </c>
       <c r="G322" s="1">
-        <v>0.078657634718</v>
+        <v>7.8657634717999997E-2</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -9430,7 +8824,7 @@
         <v>9</v>
       </c>
       <c r="G323" s="1">
-        <v>0.031379501323</v>
+        <v>3.1379501322999999E-2</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -9453,7 +8847,7 @@
         <v>9</v>
       </c>
       <c r="G324" s="1">
-        <v>0.037929706196</v>
+        <v>3.7929706196000001E-2</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -9476,7 +8870,7 @@
         <v>9</v>
       </c>
       <c r="G325" s="1">
-        <v>0.070507319574</v>
+        <v>7.0507319573999999E-2</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -9499,7 +8893,7 @@
         <v>9</v>
       </c>
       <c r="G326" s="1">
-        <v>0.064</v>
+        <v>6.4000000000000001E-2</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -9545,7 +8939,7 @@
         <v>9</v>
       </c>
       <c r="G328" s="1">
-        <v>0.051473446</v>
+        <v>5.1473445999999999E-2</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -9568,7 +8962,7 @@
         <v>9</v>
       </c>
       <c r="G329" s="1">
-        <v>0.0377401508</v>
+        <v>3.7740150799999997E-2</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -9614,7 +9008,7 @@
         <v>9</v>
       </c>
       <c r="G331" s="1">
-        <v>0.0756132562</v>
+        <v>7.5613256200000006E-2</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -9637,7 +9031,7 @@
         <v>9</v>
       </c>
       <c r="G332" s="1">
-        <v>0.0913968824</v>
+        <v>9.1396882400000004E-2</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -9660,7 +9054,7 @@
         <v>9</v>
       </c>
       <c r="G333" s="1">
-        <v>0.1698971556</v>
+        <v>0.16989715559999999</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -9683,7 +9077,7 @@
         <v>9</v>
       </c>
       <c r="G334" s="1">
-        <v>0.04384</v>
+        <v>4.3839999999999997E-2</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -9729,7 +9123,7 @@
         <v>9</v>
       </c>
       <c r="G336" s="1">
-        <v>0.03525931051</v>
+        <v>3.5259310510000003E-2</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -9752,7 +9146,7 @@
         <v>9</v>
       </c>
       <c r="G337" s="1">
-        <v>0.025852003298</v>
+        <v>2.5852003298000002E-2</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -9775,7 +9169,7 @@
         <v>9</v>
       </c>
       <c r="G338" s="1">
-        <v>0.129832481402</v>
+        <v>0.12983248140199999</v>
       </c>
     </row>
     <row r="339" spans="1:7">
@@ -9798,7 +9192,7 @@
         <v>9</v>
       </c>
       <c r="G339" s="1">
-        <v>0.051795080497</v>
+        <v>5.1795080496999997E-2</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -9821,7 +9215,7 @@
         <v>9</v>
       </c>
       <c r="G340" s="1">
-        <v>0.062606864444</v>
+        <v>6.2606864444000002E-2</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -9867,7 +9261,7 @@
         <v>9</v>
       </c>
       <c r="G342" s="1">
-        <v>0.06588</v>
+        <v>6.5879999999999994E-2</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -9890,7 +9284,7 @@
         <v>9</v>
       </c>
       <c r="G343" s="1">
-        <v>0.32574</v>
+        <v>0.32573999999999997</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -9913,7 +9307,7 @@
         <v>9</v>
       </c>
       <c r="G344" s="1">
-        <v>0.0026720623</v>
+        <v>2.6720622999999999E-3</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -9936,7 +9330,7 @@
         <v>9</v>
       </c>
       <c r="G345" s="1">
-        <v>0.007115139613</v>
+        <v>7.1151396130000001E-3</v>
       </c>
     </row>
     <row r="346" spans="1:7">
@@ -9959,7 +9353,7 @@
         <v>9</v>
       </c>
       <c r="G346" s="1">
-        <v>0.017852953692</v>
+        <v>1.7852953692E-2</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -9982,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="G347" s="1">
-        <v>0.005927202006</v>
+        <v>5.9272020060000003E-3</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -10005,7 +9399,7 @@
         <v>9</v>
       </c>
       <c r="G348" s="1">
-        <v>0.005962875843</v>
+        <v>5.962875843E-3</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -10028,7 +9422,7 @@
         <v>9</v>
       </c>
       <c r="G349" s="1">
-        <v>0.004774938236</v>
+        <v>4.7749382360000002E-3</v>
       </c>
     </row>
     <row r="350" spans="1:7">
@@ -10051,7 +9445,7 @@
         <v>9</v>
       </c>
       <c r="G350" s="1">
-        <v>0.06102</v>
+        <v>6.1019999999999998E-2</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -10074,7 +9468,7 @@
         <v>9</v>
       </c>
       <c r="G351" s="1">
-        <v>0.30171</v>
+        <v>0.30170999999999998</v>
       </c>
     </row>
     <row r="352" spans="1:7">
@@ -10097,7 +9491,7 @@
         <v>9</v>
       </c>
       <c r="G352" s="1">
-        <v>0.00247494295</v>
+        <v>2.47494295E-3</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -10120,7 +9514,7 @@
         <v>9</v>
       </c>
       <c r="G353" s="1">
-        <v>0.0065902522645</v>
+        <v>6.5902522644999996E-3</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -10143,7 +9537,7 @@
         <v>9</v>
       </c>
       <c r="G354" s="1">
-        <v>0.016535932518</v>
+        <v>1.6535932518E-2</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -10166,7 +9560,7 @@
         <v>9</v>
       </c>
       <c r="G355" s="1">
-        <v>0.005489949399</v>
+        <v>5.4899493989999998E-3</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -10189,7 +9583,7 @@
         <v>9</v>
       </c>
       <c r="G356" s="1">
-        <v>0.0055229915595</v>
+        <v>5.5229915594999998E-3</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -10212,7 +9606,7 @@
         <v>9</v>
       </c>
       <c r="G357" s="1">
-        <v>0.004422688694</v>
+        <v>4.422688694E-3</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -10235,7 +9629,7 @@
         <v>9</v>
       </c>
       <c r="G358" s="1">
-        <v>0.674506875</v>
+        <v>0.67450687499999995</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -10258,7 +9652,7 @@
         <v>9</v>
       </c>
       <c r="G359" s="1">
-        <v>1.0293315</v>
+        <v>1.0293315000000001</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -10281,7 +9675,7 @@
         <v>9</v>
       </c>
       <c r="G360" s="1">
-        <v>0.0139671978479625</v>
+        <v>1.3967197847962499E-2</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -10327,7 +9721,7 @@
         <v>9</v>
       </c>
       <c r="G362" s="1">
-        <v>0.226725</v>
+        <v>0.22672500000000001</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -10419,7 +9813,7 @@
         <v>9</v>
       </c>
       <c r="G366" s="1">
-        <v>10.0431309859028</v>
+        <v>10.043130985902801</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -10442,7 +9836,7 @@
         <v>9</v>
       </c>
       <c r="G367" s="1">
-        <v>5.59102137359535</v>
+        <v>5.5910213735953498</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -10465,7 +9859,7 @@
         <v>9</v>
       </c>
       <c r="G368" s="1">
-        <v>5.28040907506227</v>
+        <v>5.2804090750622699</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -10488,7 +9882,7 @@
         <v>9</v>
       </c>
       <c r="G369" s="1">
-        <v>0.62122459706615</v>
+        <v>0.62122459706614996</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -10557,7 +9951,7 @@
         <v>9</v>
       </c>
       <c r="G372" s="1">
-        <v>0.828299462754866</v>
+        <v>0.82829946275486599</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -10580,7 +9974,7 @@
         <v>9</v>
       </c>
       <c r="G373" s="1">
-        <v>9.83605612021404</v>
+        <v>9.8360561202140406</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -10603,7 +9997,7 @@
         <v>9</v>
       </c>
       <c r="G374" s="1">
-        <v>1.8761160902247</v>
+        <v>1.8761160902247001</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -10626,7 +10020,7 @@
         <v>9</v>
       </c>
       <c r="G375" s="1">
-        <v>0.851538128330141</v>
+        <v>0.85153812833014098</v>
       </c>
     </row>
     <row r="376" spans="1:7">
@@ -10649,7 +10043,7 @@
         <v>9</v>
       </c>
       <c r="G376" s="1">
-        <v>8.67580408436974</v>
+        <v>8.6758040843697408</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -10672,7 +10066,7 @@
         <v>9</v>
       </c>
       <c r="G377" s="1">
-        <v>0.402934505736019</v>
+        <v>0.40293450573601902</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -10718,7 +10112,7 @@
         <v>9</v>
       </c>
       <c r="G379" s="1">
-        <v>2.86484571007519</v>
+        <v>2.8648457100751901</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -10741,7 +10135,7 @@
         <v>9</v>
       </c>
       <c r="G380" s="1">
-        <v>6.48147159642795</v>
+        <v>6.4814715964279497</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -10764,7 +10158,7 @@
         <v>9</v>
       </c>
       <c r="G381" s="1">
-        <v>0.554174637627073</v>
+        <v>0.55417463762707297</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -10787,7 +10181,7 @@
         <v>9</v>
       </c>
       <c r="G382" s="1">
-        <v>2.19805482188229</v>
+        <v>2.1980548218822902</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -10833,7 +10227,7 @@
         <v>9</v>
       </c>
       <c r="G384" s="1">
-        <v>4.80754615162455</v>
+        <v>4.8075461516245497</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -10879,7 +10273,7 @@
         <v>9</v>
       </c>
       <c r="G386" s="1">
-        <v>14.6462452526236</v>
+        <v>14.646245252623601</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -10925,7 +10319,7 @@
         <v>9</v>
       </c>
       <c r="G388" s="1">
-        <v>6.14918693812442</v>
+        <v>6.1491869381244202</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -10948,7 +10342,7 @@
         <v>9</v>
       </c>
       <c r="G389" s="1">
-        <v>1.34164078649987</v>
+        <v>1.3416407864998701</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -10971,7 +10365,7 @@
         <v>9</v>
       </c>
       <c r="G390" s="1">
-        <v>2.4217764863835</v>
+        <v>2.4217764863835001</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -10994,7 +10388,7 @@
         <v>9</v>
       </c>
       <c r="G391" s="1">
-        <v>0.52207815506876</v>
+        <v>0.52207815506875999</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -11017,7 +10411,7 @@
         <v>9</v>
       </c>
       <c r="G392" s="1">
-        <v>0.00516784092800179</v>
+        <v>5.1678409280017899E-3</v>
       </c>
     </row>
     <row r="393" spans="1:7">
@@ -11040,7 +10434,7 @@
         <v>9</v>
       </c>
       <c r="G393" s="1">
-        <v>0.721118944710904</v>
+        <v>0.72111894471090399</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -11086,7 +10480,7 @@
         <v>9</v>
       </c>
       <c r="G395" s="1">
-        <v>0.109873478378549</v>
+        <v>0.10987347837854899</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -11109,7 +10503,7 @@
         <v>9</v>
       </c>
       <c r="G396" s="1">
-        <v>0.0597662767067327</v>
+        <v>5.97662767067327E-2</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -11132,7 +10526,7 @@
         <v>9</v>
       </c>
       <c r="G397" s="1">
-        <v>0.259115186806242</v>
+        <v>0.25911518680624201</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -11155,7 +10549,7 @@
         <v>9</v>
       </c>
       <c r="G398" s="1">
-        <v>0.0370935787763033</v>
+        <v>3.7093578776303301E-2</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -11178,7 +10572,7 @@
         <v>9</v>
       </c>
       <c r="G399" s="1">
-        <v>0.0153686950428674</v>
+        <v>1.5368695042867401E-2</v>
       </c>
     </row>
     <row r="400" spans="1:7">
@@ -11201,7 +10595,7 @@
         <v>9</v>
       </c>
       <c r="G400" s="1">
-        <v>0.00164122485680895</v>
+        <v>1.6412248568089499E-3</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -11224,7 +10618,7 @@
         <v>9</v>
       </c>
       <c r="G401" s="1">
-        <v>0.000350198976500069</v>
+        <v>3.5019897650006898E-4</v>
       </c>
     </row>
     <row r="402" spans="1:7">
@@ -11247,7 +10641,7 @@
         <v>9</v>
       </c>
       <c r="G402" s="1">
-        <v>0.0038199335726126</v>
+        <v>3.8199335726125999E-3</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -11270,7 +10664,7 @@
         <v>9</v>
       </c>
       <c r="G403" s="1">
-        <v>0.000428532958085611</v>
+        <v>4.2853295808561098E-4</v>
       </c>
     </row>
     <row r="404" spans="1:7">
@@ -11293,7 +10687,7 @@
         <v>9</v>
       </c>
       <c r="G404" s="1">
-        <v>0.000221178300947412</v>
+        <v>2.21178300947412E-4</v>
       </c>
     </row>
     <row r="405" spans="1:7">
@@ -11316,7 +10710,7 @@
         <v>9</v>
       </c>
       <c r="G405" s="1">
-        <v>0.000695790071730401</v>
+        <v>6.9579007173040097E-4</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -11339,7 +10733,7 @@
         <v>9</v>
       </c>
       <c r="G406" s="1">
-        <v>6.24549837883255e-6</v>
+        <v>6.24549837883255E-6</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -11385,7 +10779,7 @@
         <v>9</v>
       </c>
       <c r="G408" s="1">
-        <v>0.000218592443259139</v>
+        <v>2.1859244325913901E-4</v>
       </c>
     </row>
     <row r="409" spans="1:7">
@@ -11408,7 +10802,7 @@
         <v>9</v>
       </c>
       <c r="G409" s="1">
-        <v>3.74729902729953e-5</v>
+        <v>3.7472990272995301E-5</v>
       </c>
     </row>
     <row r="410" spans="1:7">
@@ -11431,7 +10825,7 @@
         <v>9</v>
       </c>
       <c r="G410" s="1">
-        <v>5.93322345989092e-5</v>
+        <v>5.9332234598909201E-5</v>
       </c>
     </row>
     <row r="411" spans="1:7">
@@ -11454,7 +10848,7 @@
         <v>9</v>
       </c>
       <c r="G411" s="1">
-        <v>0.00495823039118113</v>
+        <v>4.9582303911811301E-3</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -11500,7 +10894,7 @@
         <v>9</v>
       </c>
       <c r="G413" s="1">
-        <v>0.0834254281409156</v>
+        <v>8.3425428140915595E-2</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -11523,7 +10917,7 @@
         <v>9</v>
       </c>
       <c r="G414" s="1">
-        <v>0.000149891961091981</v>
+        <v>1.4989196109198099E-4</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -11546,7 +10940,7 @@
         <v>9</v>
       </c>
       <c r="G415" s="1">
-        <v>0.000933702007635466</v>
+        <v>9.3370200763546595E-4</v>
       </c>
     </row>
     <row r="416" spans="1:7">
@@ -11569,7 +10963,7 @@
         <v>9</v>
       </c>
       <c r="G416" s="1">
-        <v>0.000786932795732901</v>
+        <v>7.8693279573290096E-4</v>
       </c>
     </row>
     <row r="417" spans="1:7">
@@ -11592,7 +10986,7 @@
         <v>9</v>
       </c>
       <c r="G417" s="1">
-        <v>0.000412202893002948</v>
+        <v>4.1220289300294798E-4</v>
       </c>
     </row>
     <row r="418" spans="1:7">
@@ -11615,7 +11009,7 @@
         <v>9</v>
       </c>
       <c r="G418" s="1">
-        <v>0.014545765724301</v>
+        <v>1.4545765724301E-2</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -11638,7 +11032,7 @@
         <v>9</v>
       </c>
       <c r="G419" s="1">
-        <v>0.0650066322414757</v>
+        <v>6.5006632241475695E-2</v>
       </c>
     </row>
     <row r="420" spans="1:7">
@@ -11661,7 +11055,7 @@
         <v>9</v>
       </c>
       <c r="G420" s="1">
-        <v>0.0269094408349547</v>
+        <v>2.6909440834954699E-2</v>
       </c>
     </row>
     <row r="421" spans="1:7">
@@ -11684,7 +11078,7 @@
         <v>9</v>
       </c>
       <c r="G421" s="1">
-        <v>0.00287598600671762</v>
+        <v>2.87598600671762E-3</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -11707,7 +11101,7 @@
         <v>9</v>
       </c>
       <c r="G422" s="1">
-        <v>5.70814155395607</v>
+        <v>5.7081415539560698</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -11776,7 +11170,7 @@
         <v>9</v>
       </c>
       <c r="G425" s="1">
-        <v>1.0446161552521</v>
+        <v>1.0446161552521001</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -11799,7 +11193,7 @@
         <v>9</v>
       </c>
       <c r="G426" s="1">
-        <v>0.092411634918313</v>
+        <v>9.2411634918313001E-2</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -11845,7 +11239,7 @@
         <v>9</v>
       </c>
       <c r="G428" s="1">
-        <v>0.308193966327069</v>
+        <v>0.30819396632706902</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -11891,7 +11285,7 @@
         <v>9</v>
       </c>
       <c r="G430" s="1">
-        <v>0.0534</v>
+        <v>5.3400000000000003E-2</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -11914,7 +11308,7 @@
         <v>9</v>
       </c>
       <c r="G431" s="1">
-        <v>0.2136</v>
+        <v>0.21360000000000001</v>
       </c>
     </row>
     <row r="432" spans="1:7">
@@ -11937,7 +11331,7 @@
         <v>9</v>
       </c>
       <c r="G432" s="1">
-        <v>0.08744053815</v>
+        <v>8.7440538149999997E-2</v>
       </c>
     </row>
     <row r="433" spans="1:7">
@@ -11983,7 +11377,7 @@
         <v>9</v>
       </c>
       <c r="G434" s="1">
-        <v>0.00369303216</v>
+        <v>3.69303216E-3</v>
       </c>
     </row>
     <row r="435" spans="1:7">
@@ -12006,7 +11400,7 @@
         <v>9</v>
       </c>
       <c r="G435" s="1">
-        <v>1.9894900734</v>
+        <v>1.9894900734000001</v>
       </c>
     </row>
     <row r="436" spans="1:7">
@@ -12029,7 +11423,7 @@
         <v>9</v>
       </c>
       <c r="G436" s="1">
-        <v>0.06887629743</v>
+        <v>6.8876297429999997E-2</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -12052,7 +11446,7 @@
         <v>9</v>
       </c>
       <c r="G437" s="1">
-        <v>0.00121021662</v>
+        <v>1.21021662E-3</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -12075,7 +11469,7 @@
         <v>9</v>
       </c>
       <c r="G438" s="1">
-        <v>0.195</v>
+        <v>0.19500000000000001</v>
       </c>
     </row>
     <row r="439" spans="1:7">
@@ -12098,7 +11492,7 @@
         <v>9</v>
       </c>
       <c r="G439" s="1">
-        <v>0.0288</v>
+        <v>2.8799999999999999E-2</v>
       </c>
     </row>
     <row r="440" spans="1:7">
@@ -12121,7 +11515,7 @@
         <v>9</v>
       </c>
       <c r="G440" s="1">
-        <v>0.01970231445</v>
+        <v>1.9702314450000001E-2</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -12144,7 +11538,7 @@
         <v>9</v>
       </c>
       <c r="G441" s="1">
-        <v>0.01536476049</v>
+        <v>1.5364760490000001E-2</v>
       </c>
     </row>
     <row r="442" spans="1:7">
@@ -12167,7 +11561,7 @@
         <v>9</v>
       </c>
       <c r="G442" s="1">
-        <v>0.00148469874</v>
+        <v>1.4846987400000001E-3</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -12213,7 +11607,7 @@
         <v>9</v>
       </c>
       <c r="G444" s="1">
-        <v>8.109699e-5</v>
+        <v>8.1096989999999999E-5</v>
       </c>
     </row>
     <row r="445" spans="1:7">
@@ -12351,7 +11745,7 @@
         <v>9</v>
       </c>
       <c r="G450" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -12397,7 +11791,7 @@
         <v>9</v>
       </c>
       <c r="G452" s="1">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
     </row>
     <row r="453" spans="1:7">
@@ -12650,7 +12044,7 @@
         <v>9</v>
       </c>
       <c r="G463" s="1">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -12719,7 +12113,7 @@
         <v>9</v>
       </c>
       <c r="G466" s="1">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -12742,7 +12136,7 @@
         <v>9</v>
       </c>
       <c r="G467" s="1">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -12765,7 +12159,7 @@
         <v>9</v>
       </c>
       <c r="G468" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -12811,7 +12205,7 @@
         <v>9</v>
       </c>
       <c r="G470" s="1">
-        <v>1.13966011749835</v>
+        <v>1.1396601174983501</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -12834,7 +12228,7 @@
         <v>9</v>
       </c>
       <c r="G471" s="1">
-        <v>0.421639392870144</v>
+        <v>0.42163939287014401</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -12857,7 +12251,7 @@
         <v>9</v>
       </c>
       <c r="G472" s="1">
-        <v>0.122468500815727</v>
+        <v>0.12246850081572699</v>
       </c>
     </row>
     <row r="473" spans="1:7">
@@ -12880,7 +12274,7 @@
         <v>9</v>
       </c>
       <c r="G473" s="1">
-        <v>0.0797960650089252</v>
+        <v>7.9796065008925193E-2</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -12903,7 +12297,7 @@
         <v>9</v>
       </c>
       <c r="G474" s="1">
-        <v>0.0265941839013658</v>
+        <v>2.6594183901365798E-2</v>
       </c>
     </row>
     <row r="475" spans="1:7">
@@ -12926,7 +12320,7 @@
         <v>9</v>
       </c>
       <c r="G475" s="1">
-        <v>0.834480356386733</v>
+        <v>0.83448035638673301</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -12995,7 +12389,7 @@
         <v>9</v>
       </c>
       <c r="G478" s="1">
-        <v>0.0244254112752205</v>
+        <v>2.44254112752205E-2</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -13018,7 +12412,7 @@
         <v>9</v>
       </c>
       <c r="G479" s="1">
-        <v>0.197727261371639</v>
+        <v>0.19772726137163901</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -13041,7 +12435,7 @@
         <v>9</v>
       </c>
       <c r="G480" s="1">
-        <v>0.106902673814266</v>
+        <v>0.10690267381426601</v>
       </c>
     </row>
     <row r="481" spans="1:7">
@@ -13110,7 +12504,7 @@
         <v>9</v>
       </c>
       <c r="G483" s="1">
-        <v>0.296067292833982</v>
+        <v>0.29606729283398198</v>
       </c>
     </row>
     <row r="484" spans="1:7">
@@ -13156,7 +12550,7 @@
         <v>9</v>
       </c>
       <c r="G485" s="1">
-        <v>0.301388283254709</v>
+        <v>0.30138828325470901</v>
       </c>
     </row>
     <row r="486" spans="1:7">
@@ -13179,7 +12573,7 @@
         <v>9</v>
       </c>
       <c r="G486" s="1">
-        <v>0.475669529717471</v>
+        <v>0.47566952971747101</v>
       </c>
     </row>
     <row r="487" spans="1:7">
@@ -13225,7 +12619,7 @@
         <v>9</v>
       </c>
       <c r="G488" s="1">
-        <v>0.720284461877414</v>
+        <v>0.72028446187741402</v>
       </c>
     </row>
     <row r="489" spans="1:7">
@@ -13248,7 +12642,7 @@
         <v>9</v>
       </c>
       <c r="G489" s="1">
-        <v>8.72</v>
+        <v>8.7200000000000006</v>
       </c>
     </row>
     <row r="490" spans="1:7">
@@ -13271,7 +12665,7 @@
         <v>9</v>
       </c>
       <c r="G490" s="1">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
     </row>
     <row r="491" spans="1:7">
@@ -13432,7 +12826,7 @@
         <v>9</v>
       </c>
       <c r="G497" s="1">
-        <v>0.0488</v>
+        <v>4.8800000000000003E-2</v>
       </c>
     </row>
     <row r="498" spans="1:7">
@@ -13455,7 +12849,7 @@
         <v>9</v>
       </c>
       <c r="G498" s="1">
-        <v>0.044</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -13478,7 +12872,7 @@
         <v>9</v>
       </c>
       <c r="G499" s="1">
-        <v>0.00715659848</v>
+        <v>7.1565984799999999E-3</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -13616,7 +13010,7 @@
         <v>9</v>
       </c>
       <c r="G505" s="1">
-        <v>0.0329089653438087</v>
+        <v>3.2908965343808702E-2</v>
       </c>
     </row>
     <row r="506" spans="1:7">
@@ -13662,7 +13056,7 @@
         <v>9</v>
       </c>
       <c r="G507" s="1">
-        <v>0.0228315918142762</v>
+        <v>2.28315918142762E-2</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -13685,7 +13079,7 @@
         <v>9</v>
       </c>
       <c r="G508" s="1">
-        <v>0.00532189931133613</v>
+        <v>5.3218993113361302E-3</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -13708,7 +13102,7 @@
         <v>9</v>
       </c>
       <c r="G509" s="1">
-        <v>0.0540545344229325</v>
+        <v>5.4054534422932503E-2</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -13731,7 +13125,7 @@
         <v>9</v>
       </c>
       <c r="G510" s="1">
-        <v>0.00334528292973853</v>
+        <v>3.3452829297385299E-3</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -13754,7 +13148,7 @@
         <v>9</v>
       </c>
       <c r="G511" s="1">
-        <v>0.00447076954449679</v>
+        <v>4.47076954449679E-3</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -13800,7 +13194,7 @@
         <v>9</v>
       </c>
       <c r="G513" s="1">
-        <v>3.04840942132122e-5</v>
+        <v>3.0484094213212201E-5</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -13823,7 +13217,7 @@
         <v>9</v>
       </c>
       <c r="G514" s="1">
-        <v>0.00253017981969662</v>
+        <v>2.5301798196966201E-3</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -13846,7 +13240,7 @@
         <v>9</v>
       </c>
       <c r="G515" s="1">
-        <v>0.000169048158818722</v>
+        <v>1.6904815881872199E-4</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -13869,7 +13263,7 @@
         <v>9</v>
       </c>
       <c r="G516" s="1">
-        <v>0.000476660382242955</v>
+        <v>4.7666038224295501E-4</v>
       </c>
     </row>
     <row r="517" spans="1:7">
@@ -13892,7 +13286,7 @@
         <v>9</v>
       </c>
       <c r="G517" s="1">
-        <v>0.00252879417905056</v>
+        <v>2.52879417905056E-3</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -13915,7 +13309,7 @@
         <v>9</v>
       </c>
       <c r="G518" s="1">
-        <v>0.0123044966272749</v>
+        <v>1.23044966272749E-2</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -13938,7 +13332,7 @@
         <v>9</v>
       </c>
       <c r="G519" s="1">
-        <v>0.00655728198639944</v>
+        <v>6.5572819863994403E-3</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -13961,7 +13355,7 @@
         <v>9</v>
       </c>
       <c r="G520" s="1">
-        <v>0.0455940010159659</v>
+        <v>4.5594001015965897E-2</v>
       </c>
     </row>
     <row r="521" spans="1:7">
@@ -14007,7 +13401,7 @@
         <v>9</v>
       </c>
       <c r="G522" s="1">
-        <v>4.9827</v>
+        <v>4.9827000000000004</v>
       </c>
     </row>
     <row r="523" spans="1:7">
@@ -14053,7 +13447,7 @@
         <v>9</v>
       </c>
       <c r="G524" s="1">
-        <v>0.5862</v>
+        <v>0.58620000000000005</v>
       </c>
     </row>
     <row r="525" spans="1:7">
@@ -14076,7 +13470,7 @@
         <v>9</v>
       </c>
       <c r="G525" s="1">
-        <v>0.1954</v>
+        <v>0.19539999999999999</v>
       </c>
     </row>
     <row r="526" spans="1:7">
@@ -14099,7 +13493,7 @@
         <v>9</v>
       </c>
       <c r="G526" s="1">
-        <v>8.1091</v>
+        <v>8.1090999999999998</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -14122,7 +13516,7 @@
         <v>9</v>
       </c>
       <c r="G527" s="1">
-        <v>0.5862</v>
+        <v>0.58620000000000005</v>
       </c>
     </row>
     <row r="528" spans="1:7">
@@ -14145,7 +13539,7 @@
         <v>9</v>
       </c>
       <c r="G528" s="1">
-        <v>0.1954</v>
+        <v>0.19539999999999999</v>
       </c>
     </row>
     <row r="529" spans="1:7">
@@ -14168,7 +13562,7 @@
         <v>9</v>
       </c>
       <c r="G529" s="1">
-        <v>0.344881</v>
+        <v>0.34488099999999999</v>
       </c>
     </row>
     <row r="530" spans="1:7">
@@ -14214,7 +13608,7 @@
         <v>9</v>
       </c>
       <c r="G531" s="1">
-        <v>0.0310308852598</v>
+        <v>3.1030885259799999E-2</v>
       </c>
     </row>
     <row r="532" spans="1:7">
@@ -14237,7 +13631,7 @@
         <v>9</v>
       </c>
       <c r="G532" s="1">
-        <v>0.0316226542575</v>
+        <v>3.1622654257500001E-2</v>
       </c>
     </row>
     <row r="533" spans="1:7">
@@ -14260,7 +13654,7 @@
         <v>9</v>
       </c>
       <c r="G533" s="1">
-        <v>0.0622836839548</v>
+        <v>6.2283683954800002E-2</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -14283,7 +13677,7 @@
         <v>9</v>
       </c>
       <c r="G534" s="1">
-        <v>0.7349400735847</v>
+        <v>0.73494007358470004</v>
       </c>
     </row>
     <row r="535" spans="1:7">
@@ -14306,7 +13700,7 @@
         <v>9</v>
       </c>
       <c r="G535" s="1">
-        <v>0.0211927262226</v>
+        <v>2.1192726222599999E-2</v>
       </c>
     </row>
     <row r="536" spans="1:7">
@@ -14329,7 +13723,7 @@
         <v>9</v>
       </c>
       <c r="G536" s="1">
-        <v>0.0159407765512</v>
+        <v>1.5940776551199999E-2</v>
       </c>
     </row>
     <row r="537" spans="1:7">
@@ -14352,7 +13746,7 @@
         <v>9</v>
       </c>
       <c r="G537" s="1">
-        <v>184.314</v>
+        <v>184.31399999999999</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -14375,7 +13769,7 @@
         <v>9</v>
       </c>
       <c r="G538" s="1">
-        <v>67.782</v>
+        <v>67.781999999999996</v>
       </c>
     </row>
     <row r="539" spans="1:7">
@@ -14398,7 +13792,7 @@
         <v>9</v>
       </c>
       <c r="G539" s="1">
-        <v>160.8</v>
+        <v>160.80000000000001</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -14536,7 +13930,7 @@
         <v>9</v>
       </c>
       <c r="G545" s="1">
-        <v>0.0645</v>
+        <v>6.4500000000000002E-2</v>
       </c>
     </row>
     <row r="546" spans="1:7">
@@ -14559,7 +13953,7 @@
         <v>9</v>
       </c>
       <c r="G546" s="1">
-        <v>0.0117</v>
+        <v>1.17E-2</v>
       </c>
     </row>
     <row r="547" spans="1:7">
@@ -14582,7 +13976,7 @@
         <v>9</v>
       </c>
       <c r="G547" s="1">
-        <v>0.13477060608</v>
+        <v>0.13477060607999999</v>
       </c>
     </row>
     <row r="548" spans="1:7">
@@ -14605,7 +13999,7 @@
         <v>9</v>
       </c>
       <c r="G548" s="1">
-        <v>0.0288143442</v>
+        <v>2.8814344200000001E-2</v>
       </c>
     </row>
     <row r="549" spans="1:7">
@@ -14628,7 +14022,7 @@
         <v>9</v>
       </c>
       <c r="G549" s="1">
-        <v>0.07534540098</v>
+        <v>7.5345400980000005E-2</v>
       </c>
     </row>
     <row r="550" spans="1:7">
@@ -14674,7 +14068,7 @@
         <v>9</v>
       </c>
       <c r="G551" s="1">
-        <v>0.0367394037</v>
+        <v>3.6739403699999999E-2</v>
       </c>
     </row>
     <row r="552" spans="1:7">
@@ -14697,7 +14091,7 @@
         <v>9</v>
       </c>
       <c r="G552" s="1">
-        <v>0.02619601665</v>
+        <v>2.6196016650000001E-2</v>
       </c>
     </row>
     <row r="553" spans="1:7">
@@ -14720,7 +14114,7 @@
         <v>9</v>
       </c>
       <c r="G553" s="1">
-        <v>0.0414</v>
+        <v>4.1399999999999999E-2</v>
       </c>
     </row>
     <row r="554" spans="1:7">
@@ -14766,7 +14160,7 @@
         <v>9</v>
       </c>
       <c r="G555" s="1">
-        <v>0.0010342248</v>
+        <v>1.0342248000000001E-3</v>
       </c>
     </row>
     <row r="556" spans="1:7">
@@ -14789,7 +14183,7 @@
         <v>9</v>
       </c>
       <c r="G556" s="1">
-        <v>0.0867</v>
+        <v>8.6699999999999999E-2</v>
       </c>
     </row>
     <row r="557" spans="1:7">
@@ -14812,7 +14206,7 @@
         <v>9</v>
       </c>
       <c r="G557" s="1">
-        <v>0.0192</v>
+        <v>1.9199999999999998E-2</v>
       </c>
     </row>
     <row r="558" spans="1:7">
@@ -14835,7 +14229,7 @@
         <v>9</v>
       </c>
       <c r="G558" s="1">
-        <v>0.0239570745</v>
+        <v>2.3957074500000002E-2</v>
       </c>
     </row>
     <row r="559" spans="1:7">
@@ -14858,7 +14252,7 @@
         <v>9</v>
       </c>
       <c r="G559" s="1">
-        <v>0.0108</v>
+        <v>1.0800000000000001E-2</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -14881,7 +14275,7 @@
         <v>9</v>
       </c>
       <c r="G560" s="1">
-        <v>0.0303</v>
+        <v>3.0300000000000001E-2</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -14904,7 +14298,7 @@
         <v>9</v>
       </c>
       <c r="G561" s="1">
-        <v>0.00432456579</v>
+        <v>4.3245657900000001E-3</v>
       </c>
     </row>
     <row r="562" spans="1:7">
@@ -14927,7 +14321,7 @@
         <v>9</v>
       </c>
       <c r="G562" s="1">
-        <v>0.2163</v>
+        <v>0.21629999999999999</v>
       </c>
     </row>
     <row r="563" spans="1:7">
@@ -14950,7 +14344,7 @@
         <v>9</v>
       </c>
       <c r="G563" s="1">
-        <v>0.0147</v>
+        <v>1.47E-2</v>
       </c>
     </row>
     <row r="564" spans="1:7">
@@ -14973,7 +14367,7 @@
         <v>9</v>
       </c>
       <c r="G564" s="1">
-        <v>0.01564575645</v>
+        <v>1.5645756449999999E-2</v>
       </c>
     </row>
     <row r="565" spans="1:7">
@@ -14996,7 +14390,7 @@
         <v>9</v>
       </c>
       <c r="G565" s="1">
-        <v>0.006885816</v>
+        <v>6.8858160000000003E-3</v>
       </c>
     </row>
     <row r="566" spans="1:7">
@@ -15019,7 +14413,7 @@
         <v>9</v>
       </c>
       <c r="G566" s="1">
-        <v>0.00166120311</v>
+        <v>1.66120311E-3</v>
       </c>
     </row>
     <row r="567" spans="1:7">
@@ -15042,7 +14436,7 @@
         <v>9</v>
       </c>
       <c r="G567" s="1">
-        <v>0.09920739402</v>
+        <v>9.9207394020000006E-2</v>
       </c>
     </row>
     <row r="568" spans="1:7">
@@ -15065,7 +14459,7 @@
         <v>9</v>
       </c>
       <c r="G568" s="1">
-        <v>0.00434667135</v>
+        <v>4.3466713500000002E-3</v>
       </c>
     </row>
     <row r="569" spans="1:7">
@@ -15088,7 +14482,7 @@
         <v>9</v>
       </c>
       <c r="G569" s="1">
-        <v>0.00650709612</v>
+        <v>6.5070961199999999E-3</v>
       </c>
     </row>
     <row r="570" spans="1:7">
@@ -15111,7 +14505,7 @@
         <v>9</v>
       </c>
       <c r="G570" s="1">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
     </row>
     <row r="571" spans="1:7">
@@ -15134,7 +14528,7 @@
         <v>9</v>
       </c>
       <c r="G571" s="1">
-        <v>0.0051</v>
+        <v>5.1000000000000004E-3</v>
       </c>
     </row>
     <row r="572" spans="1:7">
@@ -15157,7 +14551,7 @@
         <v>9</v>
       </c>
       <c r="G572" s="1">
-        <v>0.00078368469</v>
+        <v>7.8368469000000005E-4</v>
       </c>
     </row>
     <row r="573" spans="1:7">
@@ -15180,7 +14574,7 @@
         <v>9</v>
       </c>
       <c r="G573" s="1">
-        <v>0.00829740828</v>
+        <v>8.2974082799999998E-3</v>
       </c>
     </row>
     <row r="574" spans="1:7">
@@ -15203,7 +14597,7 @@
         <v>9</v>
       </c>
       <c r="G574" s="1">
-        <v>0.01528651152</v>
+        <v>1.5286511520000001E-2</v>
       </c>
     </row>
     <row r="575" spans="1:7">
@@ -15249,7 +14643,7 @@
         <v>9</v>
       </c>
       <c r="G576" s="1">
-        <v>0.01338430485</v>
+        <v>1.3384304850000001E-2</v>
       </c>
     </row>
     <row r="577" spans="1:7">
@@ -15272,7 +14666,7 @@
         <v>9</v>
       </c>
       <c r="G577" s="1">
-        <v>0.0027543264</v>
+        <v>2.7543263999999998E-3</v>
       </c>
     </row>
     <row r="578" spans="1:7">
@@ -15295,7 +14689,7 @@
         <v>9</v>
       </c>
       <c r="G578" s="1">
-        <v>0.0705</v>
+        <v>7.0499999999999993E-2</v>
       </c>
     </row>
     <row r="579" spans="1:7">
@@ -15318,7 +14712,7 @@
         <v>9</v>
       </c>
       <c r="G579" s="1">
-        <v>0.0687</v>
+        <v>6.8699999999999997E-2</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -15341,7 +14735,7 @@
         <v>9</v>
       </c>
       <c r="G580" s="1">
-        <v>0.00683670699</v>
+        <v>6.8367069900000001E-3</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -15364,7 +14758,7 @@
         <v>9</v>
       </c>
       <c r="G581" s="1">
-        <v>0.00298672269</v>
+        <v>2.9867226900000001E-3</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -15387,7 +14781,7 @@
         <v>9</v>
       </c>
       <c r="G582" s="1">
-        <v>0.005164362</v>
+        <v>5.1643619999999996E-3</v>
       </c>
     </row>
     <row r="583" spans="1:7">
@@ -15433,7 +14827,7 @@
         <v>9</v>
       </c>
       <c r="G584" s="1">
-        <v>0.00467374761</v>
+        <v>4.67374761E-3</v>
       </c>
     </row>
     <row r="585" spans="1:7">
@@ -15456,7 +14850,7 @@
         <v>9</v>
       </c>
       <c r="G585" s="1">
-        <v>0.0018935994</v>
+        <v>1.8935994000000001E-3</v>
       </c>
     </row>
     <row r="586" spans="1:7">
@@ -15479,7 +14873,7 @@
         <v>9</v>
       </c>
       <c r="G586" s="1">
-        <v>0.500800586400854</v>
+        <v>0.50080058640085401</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -15502,7 +14896,7 @@
         <v>9</v>
       </c>
       <c r="G587" s="1">
-        <v>0.188541645267034</v>
+        <v>0.18854164526703401</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -15525,7 +14919,7 @@
         <v>9</v>
       </c>
       <c r="G588" s="1">
-        <v>0.0100677763525208</v>
+        <v>1.00677763525208E-2</v>
       </c>
     </row>
     <row r="589" spans="1:7">
@@ -15548,7 +14942,7 @@
         <v>9</v>
       </c>
       <c r="G589" s="1">
-        <v>0.16783070220681</v>
+        <v>0.16783070220681001</v>
       </c>
     </row>
     <row r="590" spans="1:7">
@@ -15571,7 +14965,7 @@
         <v>9</v>
       </c>
       <c r="G590" s="1">
-        <v>0.103274463540113</v>
+        <v>0.10327446354011301</v>
       </c>
     </row>
     <row r="591" spans="1:7">
@@ -15594,7 +14988,7 @@
         <v>9</v>
       </c>
       <c r="G591" s="1">
-        <v>0.220980970820617</v>
+        <v>0.22098097082061699</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -15617,7 +15011,7 @@
         <v>9</v>
       </c>
       <c r="G592" s="1">
-        <v>0.0215704739775743</v>
+        <v>2.1570473977574299E-2</v>
       </c>
     </row>
     <row r="593" spans="1:7">
@@ -15709,7 +15103,7 @@
         <v>9</v>
       </c>
       <c r="G596" s="1">
-        <v>0.0387650316341582</v>
+        <v>3.8765031634158197E-2</v>
       </c>
     </row>
     <row r="597" spans="1:7">
@@ -15732,7 +15126,7 @@
         <v>9</v>
       </c>
       <c r="G597" s="1">
-        <v>0.00275022186579097</v>
+        <v>2.7502218657909699E-3</v>
       </c>
     </row>
     <row r="598" spans="1:7">
@@ -15778,7 +15172,7 @@
         <v>9</v>
       </c>
       <c r="G599" s="1">
-        <v>4.39872847627584</v>
+        <v>4.3987284762758403</v>
       </c>
     </row>
     <row r="600" spans="1:7">
@@ -15801,7 +15195,7 @@
         <v>9</v>
       </c>
       <c r="G600" s="1">
-        <v>1.44952200673187</v>
+        <v>1.4495220067318699</v>
       </c>
     </row>
     <row r="601" spans="1:7">
@@ -15824,7 +15218,7 @@
         <v>9</v>
       </c>
       <c r="G601" s="1">
-        <v>0.00471193783579513</v>
+        <v>4.7119378357951304E-3</v>
       </c>
     </row>
     <row r="602" spans="1:7">
@@ -15847,7 +15241,7 @@
         <v>9</v>
       </c>
       <c r="G602" s="1">
-        <v>0.208088549852725</v>
+        <v>0.20808854985272501</v>
       </c>
     </row>
     <row r="603" spans="1:7">
@@ -15870,7 +15264,7 @@
         <v>9</v>
       </c>
       <c r="G603" s="1">
-        <v>0.0569056385096262</v>
+        <v>5.6905638509626197E-2</v>
       </c>
     </row>
     <row r="604" spans="1:7">
@@ -15893,7 +15287,7 @@
         <v>9</v>
       </c>
       <c r="G604" s="1">
-        <v>5.02178123397054</v>
+        <v>5.0217812339705397</v>
       </c>
     </row>
     <row r="605" spans="1:7">
@@ -15916,7 +15310,7 @@
         <v>9</v>
       </c>
       <c r="G605" s="1">
-        <v>0.165422172289049</v>
+        <v>0.16542217228904901</v>
       </c>
     </row>
     <row r="606" spans="1:7">
@@ -15939,7 +15333,7 @@
         <v>9</v>
       </c>
       <c r="G606" s="1">
-        <v>0.301697554121948</v>
+        <v>0.30169755412194799</v>
       </c>
     </row>
     <row r="607" spans="1:7">
@@ -15962,7 +15356,7 @@
         <v>9</v>
       </c>
       <c r="G607" s="1">
-        <v>0.07935042213</v>
+        <v>7.9350422130000001E-2</v>
       </c>
     </row>
     <row r="608" spans="1:7">
@@ -15985,7 +15379,7 @@
         <v>9</v>
       </c>
       <c r="G608" s="1">
-        <v>0.04685510879</v>
+        <v>4.6855108790000002E-2</v>
       </c>
     </row>
     <row r="609" spans="1:7">
@@ -16008,7 +15402,7 @@
         <v>9</v>
       </c>
       <c r="G609" s="1">
-        <v>0.9703405838</v>
+        <v>0.97034058379999999</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -16031,7 +15425,7 @@
         <v>9</v>
       </c>
       <c r="G610" s="1">
-        <v>0.00130543595</v>
+        <v>1.3054359500000001E-3</v>
       </c>
     </row>
     <row r="611" spans="1:7">
@@ -16077,7 +15471,7 @@
         <v>9</v>
       </c>
       <c r="G612" s="1">
-        <v>0.3085467273</v>
+        <v>0.30854672729999999</v>
       </c>
     </row>
     <row r="613" spans="1:7">
@@ -16100,7 +15494,7 @@
         <v>9</v>
       </c>
       <c r="G613" s="1">
-        <v>0.7512442056</v>
+        <v>0.75124420560000005</v>
       </c>
     </row>
     <row r="614" spans="1:7">
@@ -16123,7 +15517,7 @@
         <v>9</v>
       </c>
       <c r="G614" s="1">
-        <v>0.1835322363</v>
+        <v>0.18353223630000001</v>
       </c>
     </row>
     <row r="615" spans="1:7">
@@ -16169,7 +15563,7 @@
         <v>9</v>
       </c>
       <c r="G616" s="1">
-        <v>0.0014</v>
+        <v>1.4E-3</v>
       </c>
     </row>
     <row r="617" spans="1:7">
@@ -16192,7 +15586,7 @@
         <v>9</v>
       </c>
       <c r="G617" s="1">
-        <v>0.19752472866</v>
+        <v>0.19752472866000001</v>
       </c>
     </row>
     <row r="618" spans="1:7">
@@ -16215,7 +15609,7 @@
         <v>9</v>
       </c>
       <c r="G618" s="1">
-        <v>0.537096</v>
+        <v>0.53709600000000002</v>
       </c>
     </row>
     <row r="619" spans="1:7">
@@ -16261,7 +15655,7 @@
         <v>9</v>
       </c>
       <c r="G620" s="1">
-        <v>0.248906</v>
+        <v>0.24890599999999999</v>
       </c>
     </row>
     <row r="621" spans="1:7">
@@ -16284,7 +15678,7 @@
         <v>9</v>
       </c>
       <c r="G621" s="1">
-        <v>0.038962</v>
+        <v>3.8961999999999997E-2</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -16330,7 +15724,7 @@
         <v>9</v>
       </c>
       <c r="G623" s="1">
-        <v>0.724</v>
+        <v>0.72399999999999998</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -16399,7 +15793,7 @@
         <v>9</v>
       </c>
       <c r="G626" s="1">
-        <v>3.958</v>
+        <v>3.9580000000000002</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -16422,7 +15816,7 @@
         <v>9</v>
       </c>
       <c r="G627" s="1">
-        <v>0.808</v>
+        <v>0.80800000000000005</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -16445,7 +15839,7 @@
         <v>9</v>
       </c>
       <c r="G628" s="1">
-        <v>3.805077654</v>
+        <v>3.8050776540000002</v>
       </c>
     </row>
     <row r="629" spans="1:7">
@@ -16468,7 +15862,7 @@
         <v>9</v>
       </c>
       <c r="G629" s="1">
-        <v>0.0209022744</v>
+        <v>2.09022744E-2</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -16491,7 +15885,7 @@
         <v>9</v>
       </c>
       <c r="G630" s="1">
-        <v>0.0220251238</v>
+        <v>2.2025123800000001E-2</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -16514,7 +15908,7 @@
         <v>9</v>
       </c>
       <c r="G631" s="1">
-        <v>4.577166208</v>
+        <v>4.5771662080000004</v>
       </c>
     </row>
     <row r="632" spans="1:7">
@@ -16560,7 +15954,7 @@
         <v>9</v>
       </c>
       <c r="G633" s="1">
-        <v>0.0546741308</v>
+        <v>5.4674130799999998E-2</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -16606,7 +16000,7 @@
         <v>9</v>
       </c>
       <c r="G635" s="1">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
     </row>
     <row r="636" spans="1:7">
@@ -16629,7 +16023,7 @@
         <v>9</v>
       </c>
       <c r="G636" s="1">
-        <v>1.0359598882</v>
+        <v>1.0359598882000001</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -16675,7 +16069,7 @@
         <v>9</v>
       </c>
       <c r="G638" s="1">
-        <v>1.428624558</v>
+        <v>1.4286245580000001</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -16698,7 +16092,7 @@
         <v>9</v>
       </c>
       <c r="G639" s="1">
-        <v>1.3119476356</v>
+        <v>1.3119476355999999</v>
       </c>
     </row>
     <row r="640" spans="1:7">
@@ -16721,7 +16115,7 @@
         <v>9</v>
       </c>
       <c r="G640" s="1">
-        <v>0.541866425</v>
+        <v>0.54186642500000004</v>
       </c>
     </row>
     <row r="641" spans="1:7">
@@ -16744,7 +16138,7 @@
         <v>9</v>
       </c>
       <c r="G641" s="1">
-        <v>0.0144705078</v>
+        <v>1.4470507800000001E-2</v>
       </c>
     </row>
     <row r="642" spans="1:7">
@@ -16790,7 +16184,7 @@
         <v>9</v>
       </c>
       <c r="G643" s="1">
-        <v>0.0020657448</v>
+        <v>2.0657447999999998E-3</v>
       </c>
     </row>
     <row r="644" spans="1:7">
@@ -16813,7 +16207,7 @@
         <v>9</v>
       </c>
       <c r="G644" s="1">
-        <v>0.0058529436</v>
+        <v>5.8529436000000004E-3</v>
       </c>
     </row>
     <row r="645" spans="1:7">
@@ -16932,29 +16326,26 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E649">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="E1:E649" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F89"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H89"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.0446428571429" customWidth="1"/>
-    <col min="2" max="2" width="22.1785714285714" customWidth="1"/>
-    <col min="3" max="3" width="11.8125" customWidth="1"/>
-    <col min="4" max="4" width="16.8035714285714" customWidth="1"/>
-    <col min="5" max="5" width="12.9375" customWidth="1"/>
-    <col min="6" max="6" width="35.8660714285714" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+    <col min="3" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -16964,17 +16355,23 @@
       <c r="C1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
@@ -16982,53 +16379,59 @@
         <v>30</v>
       </c>
       <c r="C2">
-        <v>0.23</v>
-      </c>
-      <c r="D2" s="2" t="s">
+        <v>0.18</v>
+      </c>
+      <c r="D2">
+        <v>0.9</v>
+      </c>
+      <c r="E2">
+        <v>0.05</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H2" t="s">
         <v>75</v>
       </c>
-      <c r="E2">
-        <v>0.2275</v>
-      </c>
-      <c r="F2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3">
-        <v>0.2275</v>
-      </c>
       <c r="F3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4">
-        <v>0.2275</v>
-      </c>
       <c r="F4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="5" ht="17" spans="1:6">
+      <c r="G4">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -17036,19 +16439,25 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>0.28</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>78</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D5">
+        <v>0.8</v>
       </c>
       <c r="E5">
-        <v>0.2275</v>
-      </c>
-      <c r="F5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" ht="17" spans="1:6">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -17058,17 +16467,23 @@
       <c r="C6">
         <v>0.3251</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>79</v>
+      <c r="D6">
+        <v>0.81</v>
       </c>
       <c r="E6">
-        <v>0.2275</v>
-      </c>
-      <c r="F6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" ht="17" spans="1:6">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
@@ -17076,19 +16491,25 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>0.3833</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>80</v>
+        <v>0.38329999999999997</v>
+      </c>
+      <c r="D7">
+        <v>0.95</v>
       </c>
       <c r="E7">
-        <v>0.2275</v>
-      </c>
-      <c r="F7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -17096,36 +16517,42 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>0.259</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="D8">
+        <v>0.6</v>
       </c>
       <c r="E8">
-        <v>0.2275</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9">
-        <v>0.2275</v>
-      </c>
       <c r="F9" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -17133,70 +16560,70 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10">
-        <v>0.2275</v>
+        <v>81</v>
       </c>
       <c r="F10" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11">
-        <v>0.2275</v>
-      </c>
       <c r="F11" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12">
-        <v>0.2275</v>
-      </c>
       <c r="F12" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13">
-        <v>0.2275</v>
-      </c>
       <c r="F13" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -17206,17 +16633,23 @@
       <c r="C14">
         <v>0.249</v>
       </c>
-      <c r="D14" t="s">
-        <v>81</v>
+      <c r="D14">
+        <v>0.6</v>
       </c>
       <c r="E14">
-        <v>0.2275</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>80</v>
+      </c>
+      <c r="G14">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
@@ -17224,53 +16657,59 @@
         <v>30</v>
       </c>
       <c r="C15">
-        <v>0.356</v>
-      </c>
-      <c r="D15" t="s">
-        <v>83</v>
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="D15">
+        <v>0.85</v>
       </c>
       <c r="E15">
-        <v>0.2275</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>82</v>
+      </c>
+      <c r="G15">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16">
-        <v>0.2275</v>
-      </c>
       <c r="F16" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17">
-        <v>0.2275</v>
-      </c>
       <c r="F17" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>39</v>
       </c>
@@ -17280,68 +16719,74 @@
       <c r="C18">
         <v>0.23</v>
       </c>
-      <c r="D18" t="s">
-        <v>84</v>
+      <c r="D18">
+        <v>0.9</v>
       </c>
       <c r="E18">
-        <v>0.2275</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>83</v>
+      </c>
+      <c r="G18">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19">
-        <v>0.2275</v>
-      </c>
       <c r="F19" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20">
-        <v>0.2275</v>
-      </c>
       <c r="F20" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21">
-        <v>0.2275</v>
-      </c>
       <c r="F21" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="22" ht="17" spans="1:6">
+      <c r="G21">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>47</v>
       </c>
@@ -17351,17 +16796,23 @@
       <c r="C22">
         <v>0.3</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>85</v>
+      <c r="D22">
+        <v>0.9</v>
       </c>
       <c r="E22">
-        <v>0.2275</v>
-      </c>
-      <c r="F22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -17369,36 +16820,42 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>0.28</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D23">
+        <v>0.8</v>
       </c>
       <c r="E23">
-        <v>0.2275</v>
-      </c>
-      <c r="F23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24">
-        <v>0.2275</v>
-      </c>
       <c r="F24" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="25" ht="17" spans="1:6">
+      <c r="G24">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
@@ -17408,17 +16865,23 @@
       <c r="C25">
         <v>0.3</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>85</v>
+      <c r="D25">
+        <v>0.9</v>
       </c>
       <c r="E25">
-        <v>0.2275</v>
-      </c>
-      <c r="F25" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" ht="17" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -17428,17 +16891,23 @@
       <c r="C26">
         <v>0.3</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>85</v>
+      <c r="D26">
+        <v>0.9</v>
       </c>
       <c r="E26">
-        <v>0.2275</v>
-      </c>
-      <c r="F26" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" ht="17" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
@@ -17448,17 +16917,23 @@
       <c r="C27">
         <v>0.3</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>85</v>
+      <c r="D27">
+        <v>0.9</v>
       </c>
       <c r="E27">
-        <v>0.2275</v>
-      </c>
-      <c r="F27" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" ht="17" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
         <v>43</v>
       </c>
@@ -17468,17 +16943,23 @@
       <c r="C28">
         <v>0.3</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>85</v>
+      <c r="D28">
+        <v>0.9</v>
       </c>
       <c r="E28">
-        <v>0.2275</v>
-      </c>
-      <c r="F28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" ht="17" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -17488,68 +16969,74 @@
       <c r="C29">
         <v>0.09</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>87</v>
+      <c r="D29">
+        <v>0.8</v>
       </c>
       <c r="E29">
-        <v>0.2275</v>
-      </c>
-      <c r="F29" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D30" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30">
-        <v>0.2275</v>
-      </c>
       <c r="F30" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31">
-        <v>0.2275</v>
-      </c>
       <c r="F31" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D32" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32">
-        <v>0.2275</v>
-      </c>
       <c r="F32" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
@@ -17557,36 +17044,42 @@
         <v>30</v>
       </c>
       <c r="C33">
-        <v>0.231</v>
-      </c>
-      <c r="D33" t="s">
-        <v>81</v>
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="D33">
+        <v>0.6</v>
       </c>
       <c r="E33">
-        <v>0.2275</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="F33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>80</v>
+      </c>
+      <c r="G33">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34">
-        <v>0.2275</v>
-      </c>
       <c r="F34" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>59</v>
       </c>
@@ -17594,104 +17087,110 @@
         <v>30</v>
       </c>
       <c r="C35">
-        <v>0.356</v>
-      </c>
-      <c r="D35" t="s">
-        <v>83</v>
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="D35">
+        <v>0.85</v>
       </c>
       <c r="E35">
-        <v>0.2275</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>82</v>
+      </c>
+      <c r="G35">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H35" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D36" t="s">
-        <v>77</v>
-      </c>
-      <c r="E36">
-        <v>0.2275</v>
-      </c>
       <c r="F36" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D37" t="s">
-        <v>77</v>
-      </c>
-      <c r="E37">
-        <v>0.2275</v>
-      </c>
       <c r="F37" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D38" t="s">
-        <v>77</v>
-      </c>
-      <c r="E38">
-        <v>0.2275</v>
-      </c>
       <c r="F38" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D39" t="s">
-        <v>77</v>
-      </c>
-      <c r="E39">
-        <v>0.2275</v>
-      </c>
       <c r="F39" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D40" t="s">
-        <v>77</v>
-      </c>
-      <c r="E40">
-        <v>0.2275</v>
-      </c>
       <c r="F40" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="41" ht="17" spans="1:6">
+      <c r="G40">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
@@ -17701,34 +17200,40 @@
       <c r="C41">
         <v>0.09</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>87</v>
+      <c r="D41">
+        <v>0.8</v>
       </c>
       <c r="E41">
-        <v>0.2275</v>
-      </c>
-      <c r="F41" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>0.08</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G41">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H41" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D42" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42">
-        <v>0.2275</v>
-      </c>
       <c r="F42" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="43" ht="17" spans="1:6">
+      <c r="G42">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H42" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
@@ -17736,19 +17241,25 @@
         <v>30</v>
       </c>
       <c r="C43">
-        <v>0.45</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>88</v>
+        <v>0.42</v>
+      </c>
+      <c r="D43">
+        <v>0.9</v>
       </c>
       <c r="E43">
-        <v>0.2275</v>
-      </c>
-      <c r="F43" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>0.05</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
         <v>25</v>
       </c>
@@ -17756,19 +17267,25 @@
         <v>30</v>
       </c>
       <c r="C44">
-        <v>0.231</v>
-      </c>
-      <c r="D44" t="s">
-        <v>81</v>
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="D44">
+        <v>0.6</v>
       </c>
       <c r="E44">
-        <v>0.2275</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="F44" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>80</v>
+      </c>
+      <c r="G44">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
         <v>25</v>
       </c>
@@ -17776,19 +17293,25 @@
         <v>30</v>
       </c>
       <c r="C45">
-        <v>0.231</v>
-      </c>
-      <c r="D45" t="s">
-        <v>81</v>
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="D45">
+        <v>0.6</v>
       </c>
       <c r="E45">
-        <v>0.2275</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" ht="17" spans="1:6">
+        <v>80</v>
+      </c>
+      <c r="G45">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
         <v>25</v>
       </c>
@@ -17798,68 +17321,74 @@
       <c r="C46">
         <v>0.36</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>89</v>
+      <c r="D46">
+        <v>0.65369999999999995</v>
       </c>
       <c r="E46">
-        <v>0.2275</v>
-      </c>
-      <c r="F46" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H46" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D47" t="s">
-        <v>77</v>
-      </c>
-      <c r="E47">
-        <v>0.2275</v>
-      </c>
       <c r="F47" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H47" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48">
-        <v>0.2275</v>
-      </c>
       <c r="F48" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D49" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49">
-        <v>0.2275</v>
-      </c>
       <c r="F49" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="50" ht="17" spans="1:6">
+      <c r="G49">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H49" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
         <v>29</v>
       </c>
@@ -17867,138 +17396,144 @@
         <v>70</v>
       </c>
       <c r="C50">
-        <v>0.23</v>
-      </c>
-      <c r="D50" s="2" t="s">
+        <v>0.18</v>
+      </c>
+      <c r="D50">
+        <v>0.9</v>
+      </c>
+      <c r="E50">
+        <v>0.05</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H50" t="s">
         <v>75</v>
       </c>
-      <c r="E50">
-        <v>0.2275</v>
-      </c>
-      <c r="F50" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D51" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51">
-        <v>0.2275</v>
-      </c>
       <c r="F51" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H51" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D52" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52">
-        <v>0.2275</v>
-      </c>
       <c r="F52" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D53" t="s">
-        <v>77</v>
-      </c>
-      <c r="E53">
-        <v>0.2275</v>
-      </c>
       <c r="F53" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D54" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54">
-        <v>0.2275</v>
-      </c>
       <c r="F54" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D55" t="s">
-        <v>77</v>
-      </c>
-      <c r="E55">
-        <v>0.2275</v>
-      </c>
       <c r="F55" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H55" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D56" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56">
-        <v>0.2275</v>
-      </c>
       <c r="F56" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H56" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D57" t="s">
-        <v>77</v>
-      </c>
-      <c r="E57">
-        <v>0.2275</v>
-      </c>
       <c r="F57" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H57" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
         <v>39</v>
       </c>
@@ -18008,17 +17543,23 @@
       <c r="C58">
         <v>0.23</v>
       </c>
-      <c r="D58" t="s">
-        <v>84</v>
+      <c r="D58">
+        <v>0.9</v>
       </c>
       <c r="E58">
-        <v>0.2275</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F58" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>83</v>
+      </c>
+      <c r="G58">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H58" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
         <v>46</v>
       </c>
@@ -18026,257 +17567,263 @@
         <v>70</v>
       </c>
       <c r="C59">
-        <v>0.356</v>
-      </c>
-      <c r="D59" t="s">
-        <v>83</v>
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="D59">
+        <v>0.85</v>
       </c>
       <c r="E59">
-        <v>0.2275</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F59" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>82</v>
+      </c>
+      <c r="G59">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H59" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D60" t="s">
-        <v>77</v>
-      </c>
-      <c r="E60">
-        <v>0.2275</v>
-      </c>
       <c r="F60" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H60" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D61" t="s">
-        <v>77</v>
-      </c>
-      <c r="E61">
-        <v>0.2275</v>
-      </c>
       <c r="F61" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D62" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62">
-        <v>0.2275</v>
-      </c>
       <c r="F62" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="G62">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D63" t="s">
-        <v>77</v>
-      </c>
-      <c r="E63">
-        <v>0.2275</v>
-      </c>
       <c r="F63" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H63" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D64" t="s">
-        <v>77</v>
-      </c>
-      <c r="E64">
-        <v>0.2275</v>
-      </c>
       <c r="F64" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H64" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D65" t="s">
-        <v>77</v>
-      </c>
-      <c r="E65">
-        <v>0.2275</v>
-      </c>
       <c r="F65" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H65" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D66" t="s">
-        <v>77</v>
-      </c>
-      <c r="E66">
-        <v>0.2275</v>
-      </c>
       <c r="F66" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H66" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D67" t="s">
-        <v>77</v>
-      </c>
-      <c r="E67">
-        <v>0.2275</v>
-      </c>
       <c r="F67" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H67" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D68" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68">
-        <v>0.2275</v>
-      </c>
       <c r="F68" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H68" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D69" t="s">
-        <v>77</v>
-      </c>
-      <c r="E69">
-        <v>0.2275</v>
-      </c>
       <c r="F69" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D70" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70">
-        <v>0.2275</v>
-      </c>
       <c r="F70" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D71" t="s">
-        <v>77</v>
-      </c>
-      <c r="E71">
-        <v>0.2275</v>
-      </c>
       <c r="F71" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H71" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D72" t="s">
-        <v>77</v>
-      </c>
-      <c r="E72">
-        <v>0.2275</v>
-      </c>
       <c r="F72" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D73" t="s">
-        <v>77</v>
-      </c>
-      <c r="E73">
-        <v>0.2275</v>
-      </c>
       <c r="F73" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="74" ht="17" spans="1:6">
+      <c r="G73">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H73" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
         <v>47</v>
       </c>
@@ -18286,34 +17833,40 @@
       <c r="C74">
         <v>0.3</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>85</v>
+      <c r="D74">
+        <v>0.9</v>
       </c>
       <c r="E74">
-        <v>0.2275</v>
-      </c>
-      <c r="F74" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H74" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D75" t="s">
-        <v>77</v>
-      </c>
-      <c r="E75">
-        <v>0.2275</v>
-      </c>
       <c r="F75" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="76" ht="17" spans="1:6">
+      <c r="G75">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
         <v>42</v>
       </c>
@@ -18323,17 +17876,23 @@
       <c r="C76">
         <v>0.3</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>85</v>
+      <c r="D76">
+        <v>0.9</v>
       </c>
       <c r="E76">
-        <v>0.2275</v>
-      </c>
-      <c r="F76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" ht="17" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G76">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
         <v>40</v>
       </c>
@@ -18343,17 +17902,23 @@
       <c r="C77">
         <v>0.3</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>85</v>
+      <c r="D77">
+        <v>0.9</v>
       </c>
       <c r="E77">
-        <v>0.2275</v>
-      </c>
-      <c r="F77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" ht="17" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H77" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
         <v>41</v>
       </c>
@@ -18363,17 +17928,23 @@
       <c r="C78">
         <v>0.3</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>85</v>
+      <c r="D78">
+        <v>0.9</v>
       </c>
       <c r="E78">
-        <v>0.2275</v>
-      </c>
-      <c r="F78" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" ht="17" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G78">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H78" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
         <v>43</v>
       </c>
@@ -18383,188 +17954,195 @@
       <c r="C79">
         <v>0.3</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>85</v>
+      <c r="D79">
+        <v>0.9</v>
       </c>
       <c r="E79">
-        <v>0.2275</v>
-      </c>
-      <c r="F79" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G79">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H79" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D80" t="s">
-        <v>77</v>
-      </c>
-      <c r="E80">
-        <v>0.2275</v>
-      </c>
       <c r="F80" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="G80">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H80" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D81" t="s">
-        <v>77</v>
-      </c>
-      <c r="E81">
-        <v>0.2275</v>
-      </c>
       <c r="F81" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H81" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D82" t="s">
-        <v>77</v>
-      </c>
-      <c r="E82">
-        <v>0.2275</v>
-      </c>
       <c r="F82" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="G82">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H82" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D83" t="s">
-        <v>77</v>
-      </c>
-      <c r="E83">
-        <v>0.2275</v>
-      </c>
       <c r="F83" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H83" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E84">
-        <v>0.2275</v>
-      </c>
       <c r="F84" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="G84">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H84" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D85" t="s">
-        <v>77</v>
-      </c>
-      <c r="E85">
-        <v>0.2275</v>
-      </c>
       <c r="F85" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="G85">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H85" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D86" t="s">
-        <v>77</v>
-      </c>
-      <c r="E86">
-        <v>0.2275</v>
-      </c>
       <c r="F86" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H86" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D87" t="s">
-        <v>77</v>
-      </c>
-      <c r="E87">
-        <v>0.2275</v>
-      </c>
       <c r="F87" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H87" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D88" t="s">
-        <v>77</v>
-      </c>
-      <c r="E88">
-        <v>0.2275</v>
-      </c>
       <c r="F88" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H88" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D89" t="s">
-        <v>77</v>
-      </c>
-      <c r="E89">
-        <v>0.2275</v>
-      </c>
       <c r="F89" t="s">
         <v>76</v>
       </c>
+      <c r="G89">
+        <v>0.22750000000000001</v>
+      </c>
+      <c r="H89" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/CTCdata.xlsx
+++ b/data/CTCdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhongxinzhi/Desktop/CTCv0.1/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECA2938-DE8E-4948-B157-5721900128DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF955756-9CCD-A44F-AAC4-BE3136912611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3709" uniqueCount="91">
   <si>
     <t>Year</t>
   </si>
@@ -352,9 +352,6 @@
   </si>
   <si>
     <t>Slow pyrolysis, 450℃, 30mins RT (Uni Hasselt)</t>
-  </si>
-  <si>
-    <t>\</t>
   </si>
   <si>
     <t>Slow pyrolysis, 450℃, 30mins RT (Medina et al., 2025)</t>
@@ -16356,10 +16353,10 @@
         <v>71</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="F1" t="s">
         <v>72</v>
@@ -16388,7 +16385,7 @@
         <v>0.05</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G2">
         <v>0.22750000000000001</v>
@@ -16559,9 +16556,6 @@
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
       <c r="F10" t="s">
         <v>76</v>
       </c>
@@ -16666,7 +16660,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15">
         <v>0.22750000000000001</v>
@@ -16726,7 +16720,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G18">
         <v>0.22750000000000001</v>
@@ -16803,7 +16797,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G22">
         <v>0.22750000000000001</v>
@@ -16829,7 +16823,7 @@
         <v>5.8700000000000002E-2</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G23">
         <v>0.22750000000000001</v>
@@ -16872,7 +16866,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G25">
         <v>0.22750000000000001</v>
@@ -16898,7 +16892,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G26">
         <v>0.22750000000000001</v>
@@ -16924,7 +16918,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G27">
         <v>0.22750000000000001</v>
@@ -16950,7 +16944,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G28">
         <v>0.22750000000000001</v>
@@ -16976,7 +16970,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G29">
         <v>0.22750000000000001</v>
@@ -17096,7 +17090,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G35">
         <v>0.22750000000000001</v>
@@ -17207,7 +17201,7 @@
         <v>0.08</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G41">
         <v>0.22750000000000001</v>
@@ -17250,7 +17244,7 @@
         <v>0.05</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G43">
         <v>0.22750000000000001</v>
@@ -17328,7 +17322,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G46">
         <v>0.22750000000000001</v>
@@ -17405,7 +17399,7 @@
         <v>0.05</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G50">
         <v>0.22750000000000001</v>
@@ -17550,7 +17544,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G58">
         <v>0.22750000000000001</v>
@@ -17576,7 +17570,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G59">
         <v>0.22750000000000001</v>
@@ -17840,7 +17834,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G74">
         <v>0.22750000000000001</v>
@@ -17883,7 +17877,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G76">
         <v>0.22750000000000001</v>
@@ -17909,7 +17903,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G77">
         <v>0.22750000000000001</v>
@@ -17935,7 +17929,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G78">
         <v>0.22750000000000001</v>
@@ -17961,7 +17955,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G79">
         <v>0.22750000000000001</v>
